--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_real_estate_development.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06866783790866511</v>
+        <v>0.06852991831389343</v>
       </c>
       <c r="C2">
-        <v>1540.15127515116</v>
+        <v>1531.814909631471</v>
       </c>
       <c r="D2">
-        <v>1215.05127515116</v>
+        <v>1222.423909631471</v>
       </c>
       <c r="E2">
-        <v>-238.7</v>
+        <v>-222.991</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.709</v>
       </c>
       <c r="G2">
         <v>325.1</v>
@@ -1707,28 +1707,28 @@
         <v>62.25</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7901627</v>
       </c>
       <c r="N2">
-        <v>62.25</v>
+        <v>61.4598373</v>
       </c>
       <c r="O2">
-        <v>15.5625</v>
+        <v>15.364959325</v>
       </c>
       <c r="P2">
-        <v>46.6875</v>
+        <v>46.094877975</v>
       </c>
       <c r="Q2">
-        <v>48.1875</v>
+        <v>47.594877975</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06866783790866511</v>
+        <v>0.06884107910494287</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241992</v>
+        <v>0.449113518093322</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>78.7812434072122</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06852991831389343</v>
+        <v>0.06839199871912179</v>
       </c>
       <c r="C3">
-        <v>1531.814909631471</v>
+        <v>1523.568561004271</v>
       </c>
       <c r="D3">
-        <v>1222.423909631471</v>
+        <v>1229.886561004271</v>
       </c>
       <c r="E3">
-        <v>-222.991</v>
+        <v>-207.282</v>
       </c>
       <c r="F3">
-        <v>15.709</v>
+        <v>31.418</v>
       </c>
       <c r="G3">
         <v>325.1</v>
@@ -1789,28 +1789,28 @@
         <v>62.25</v>
       </c>
       <c r="M3">
-        <v>0.7901627</v>
+        <v>1.5803254</v>
       </c>
       <c r="N3">
-        <v>61.4598373</v>
+        <v>60.6696746</v>
       </c>
       <c r="O3">
-        <v>15.364959325</v>
+        <v>15.16741865</v>
       </c>
       <c r="P3">
-        <v>46.094877975</v>
+        <v>45.50225595</v>
       </c>
       <c r="Q3">
-        <v>47.594877975</v>
+        <v>47.00225595</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06884107910494287</v>
+        <v>0.06901785583583855</v>
       </c>
       <c r="T3">
-        <v>0.449113518093322</v>
+        <v>0.452559225612835</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>78.7812434072122</v>
+        <v>39.39062170360611</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06839199871912179</v>
+        <v>0.06825407912435011</v>
       </c>
       <c r="C4">
-        <v>1523.568561004271</v>
+        <v>1515.413888000691</v>
       </c>
       <c r="D4">
-        <v>1229.886561004271</v>
+        <v>1237.440888000691</v>
       </c>
       <c r="E4">
-        <v>-207.282</v>
+        <v>-191.573</v>
       </c>
       <c r="F4">
-        <v>31.418</v>
+        <v>47.127</v>
       </c>
       <c r="G4">
         <v>325.1</v>
@@ -1871,28 +1871,28 @@
         <v>62.25</v>
       </c>
       <c r="M4">
-        <v>1.5803254</v>
+        <v>2.3704881</v>
       </c>
       <c r="N4">
-        <v>60.6696746</v>
+        <v>59.8795119</v>
       </c>
       <c r="O4">
-        <v>15.16741865</v>
+        <v>14.969877975</v>
       </c>
       <c r="P4">
-        <v>45.50225595</v>
+        <v>44.90963392499999</v>
       </c>
       <c r="Q4">
-        <v>47.00225595</v>
+        <v>46.40963392499999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06901785583583855</v>
+        <v>0.06919827744778362</v>
       </c>
       <c r="T4">
-        <v>0.452559225612835</v>
+        <v>0.4560759786482141</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.39062170360611</v>
+        <v>26.26041446907074</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06825407912435011</v>
+        <v>0.06811615952957845</v>
       </c>
       <c r="C5">
-        <v>1515.413888000691</v>
+        <v>1507.352590357395</v>
       </c>
       <c r="D5">
-        <v>1237.440888000691</v>
+        <v>1245.088590357395</v>
       </c>
       <c r="E5">
-        <v>-191.573</v>
+        <v>-175.864</v>
       </c>
       <c r="F5">
-        <v>47.127</v>
+        <v>62.83600000000001</v>
       </c>
       <c r="G5">
         <v>325.1</v>
@@ -1953,28 +1953,28 @@
         <v>62.25</v>
       </c>
       <c r="M5">
-        <v>2.3704881</v>
+        <v>3.1606508</v>
       </c>
       <c r="N5">
-        <v>59.8795119</v>
+        <v>59.0893492</v>
       </c>
       <c r="O5">
-        <v>14.969877975</v>
+        <v>14.7723373</v>
       </c>
       <c r="P5">
-        <v>44.90963392499999</v>
+        <v>44.3170119</v>
       </c>
       <c r="Q5">
-        <v>46.40963392499999</v>
+        <v>45.8170119</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06919827744778362</v>
+        <v>0.06938245784331089</v>
       </c>
       <c r="T5">
-        <v>0.4560759786482141</v>
+        <v>0.4596659973718304</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.26041446907074</v>
+        <v>19.69531085180305</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06811615952957845</v>
+        <v>0.0679782399348068</v>
       </c>
       <c r="C6">
-        <v>1507.352590357395</v>
+        <v>1499.386410091588</v>
       </c>
       <c r="D6">
-        <v>1245.088590357395</v>
+        <v>1252.831410091589</v>
       </c>
       <c r="E6">
-        <v>-175.864</v>
+        <v>-160.155</v>
       </c>
       <c r="F6">
-        <v>62.83600000000001</v>
+        <v>78.54500000000002</v>
       </c>
       <c r="G6">
         <v>325.1</v>
@@ -2035,28 +2035,28 @@
         <v>62.25</v>
       </c>
       <c r="M6">
-        <v>3.1606508</v>
+        <v>3.950813500000001</v>
       </c>
       <c r="N6">
-        <v>59.0893492</v>
+        <v>58.2991865</v>
       </c>
       <c r="O6">
-        <v>14.7723373</v>
+        <v>14.574796625</v>
       </c>
       <c r="P6">
-        <v>44.3170119</v>
+        <v>43.724389875</v>
       </c>
       <c r="Q6">
-        <v>45.8170119</v>
+        <v>45.224389875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06938245784331089</v>
+        <v>0.06957051572084925</v>
       </c>
       <c r="T6">
-        <v>0.4596659973718304</v>
+        <v>0.4633315954369966</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.69531085180305</v>
+        <v>15.75624868144244</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0679782399348068</v>
+        <v>0.06784032034003512</v>
       </c>
       <c r="C7">
-        <v>1499.386410091588</v>
+        <v>1491.517132823894</v>
       </c>
       <c r="D7">
-        <v>1252.831410091589</v>
+        <v>1260.671132823894</v>
       </c>
       <c r="E7">
-        <v>-160.155</v>
+        <v>-144.446</v>
       </c>
       <c r="F7">
-        <v>78.54500000000002</v>
+        <v>94.25400000000002</v>
       </c>
       <c r="G7">
         <v>325.1</v>
@@ -2117,28 +2117,28 @@
         <v>62.25</v>
       </c>
       <c r="M7">
-        <v>3.950813500000001</v>
+        <v>4.7409762</v>
       </c>
       <c r="N7">
-        <v>58.2991865</v>
+        <v>57.5090238</v>
       </c>
       <c r="O7">
-        <v>14.574796625</v>
+        <v>14.37725595</v>
       </c>
       <c r="P7">
-        <v>43.724389875</v>
+        <v>43.13176785</v>
       </c>
       <c r="Q7">
-        <v>45.224389875</v>
+        <v>44.63176785</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06957051572084925</v>
+        <v>0.06976257482982461</v>
       </c>
       <c r="T7">
-        <v>0.4633315954369966</v>
+        <v>0.4670751849503577</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.75624868144244</v>
+        <v>13.13020723453537</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06784032034003512</v>
+        <v>0.06778115074526347</v>
       </c>
       <c r="C8">
-        <v>1491.517132823894</v>
+        <v>1479.201649429732</v>
       </c>
       <c r="D8">
-        <v>1260.671132823894</v>
+        <v>1264.064649429733</v>
       </c>
       <c r="E8">
-        <v>-144.446</v>
+        <v>-128.737</v>
       </c>
       <c r="F8">
-        <v>94.254</v>
+        <v>109.963</v>
       </c>
       <c r="G8">
         <v>325.1</v>
@@ -2199,45 +2199,45 @@
         <v>62.25</v>
       </c>
       <c r="M8">
-        <v>4.7409762</v>
+        <v>5.696083399999999</v>
       </c>
       <c r="N8">
-        <v>57.5090238</v>
+        <v>56.5539166</v>
       </c>
       <c r="O8">
-        <v>14.37725595</v>
+        <v>14.13847915</v>
       </c>
       <c r="P8">
-        <v>43.13176785</v>
+        <v>42.41543745</v>
       </c>
       <c r="Q8">
-        <v>44.63176785</v>
+        <v>43.91543745</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06976257482982461</v>
+        <v>0.06995876424221878</v>
       </c>
       <c r="T8">
-        <v>0.4670751849503577</v>
+        <v>0.4708992817650814</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.13020723453537</v>
+        <v>10.92856189570539</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06778115074526346</v>
+        <v>0.06775648115049181</v>
       </c>
       <c r="C9">
-        <v>1479.201649429733</v>
+        <v>1464.912911741024</v>
       </c>
       <c r="D9">
-        <v>1264.064649429733</v>
+        <v>1265.484911741024</v>
       </c>
       <c r="E9">
-        <v>-128.737</v>
+        <v>-113.028</v>
       </c>
       <c r="F9">
-        <v>109.963</v>
+        <v>125.672</v>
       </c>
       <c r="G9">
         <v>325.1</v>
@@ -2281,45 +2281,45 @@
         <v>62.25</v>
       </c>
       <c r="M9">
-        <v>5.696083400000001</v>
+        <v>6.723452000000001</v>
       </c>
       <c r="N9">
-        <v>56.5539166</v>
+        <v>55.526548</v>
       </c>
       <c r="O9">
-        <v>14.13847915</v>
+        <v>13.881637</v>
       </c>
       <c r="P9">
-        <v>42.41543745</v>
+        <v>41.644911</v>
       </c>
       <c r="Q9">
-        <v>43.91543745</v>
+        <v>43.144911</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06995876424221878</v>
+        <v>0.07015921864183891</v>
       </c>
       <c r="T9">
-        <v>0.4708992817650814</v>
+        <v>0.4748065111192557</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.92856189570539</v>
+        <v>9.258636783604612</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06775648115049181</v>
+        <v>0.06764256155572014</v>
       </c>
       <c r="C10">
-        <v>1464.912911741024</v>
+        <v>1455.804031784977</v>
       </c>
       <c r="D10">
-        <v>1265.484911741024</v>
+        <v>1272.085031784977</v>
       </c>
       <c r="E10">
-        <v>-113.028</v>
+        <v>-97.31900000000002</v>
       </c>
       <c r="F10">
-        <v>125.672</v>
+        <v>141.381</v>
       </c>
       <c r="G10">
         <v>325.1</v>
@@ -2363,28 +2363,28 @@
         <v>62.25</v>
       </c>
       <c r="M10">
-        <v>6.723452000000001</v>
+        <v>7.5638835</v>
       </c>
       <c r="N10">
-        <v>55.526548</v>
+        <v>54.6861165</v>
       </c>
       <c r="O10">
-        <v>13.881637</v>
+        <v>13.671529125</v>
       </c>
       <c r="P10">
-        <v>41.644911</v>
+        <v>41.014587375</v>
       </c>
       <c r="Q10">
-        <v>43.144911</v>
+        <v>42.514587375</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07015921864183891</v>
+        <v>0.07036407863265949</v>
       </c>
       <c r="T10">
-        <v>0.4748065111192557</v>
+        <v>0.4787996136460492</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.258636783604612</v>
+        <v>8.229899363204099</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06764256155572014</v>
+        <v>0.06758864196094846</v>
       </c>
       <c r="C11">
-        <v>1455.804031784977</v>
+        <v>1443.243016388694</v>
       </c>
       <c r="D11">
-        <v>1272.085031784977</v>
+        <v>1275.233016388694</v>
       </c>
       <c r="E11">
-        <v>-97.31900000000002</v>
+        <v>-81.61000000000001</v>
       </c>
       <c r="F11">
-        <v>141.381</v>
+        <v>157.09</v>
       </c>
       <c r="G11">
         <v>325.1</v>
@@ -2445,45 +2445,45 @@
         <v>62.25</v>
       </c>
       <c r="M11">
-        <v>7.5638835</v>
+        <v>8.529987</v>
       </c>
       <c r="N11">
-        <v>54.6861165</v>
+        <v>53.720013</v>
       </c>
       <c r="O11">
-        <v>13.671529125</v>
+        <v>13.43000325</v>
       </c>
       <c r="P11">
-        <v>41.014587375</v>
+        <v>40.29000975</v>
       </c>
       <c r="Q11">
-        <v>42.514587375</v>
+        <v>41.79000975</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07036407863265949</v>
+        <v>0.07057349106772053</v>
       </c>
       <c r="T11">
-        <v>0.4787996136460492</v>
+        <v>0.4828814517845491</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.229899363204099</v>
+        <v>7.297783689471039</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06758864196094846</v>
+        <v>0.06748072236617682</v>
       </c>
       <c r="C12">
-        <v>1443.243016388694</v>
+        <v>1433.881712191616</v>
       </c>
       <c r="D12">
-        <v>1275.233016388694</v>
+        <v>1281.580712191616</v>
       </c>
       <c r="E12">
-        <v>-81.60999999999999</v>
+        <v>-65.90100000000001</v>
       </c>
       <c r="F12">
-        <v>157.09</v>
+        <v>172.799</v>
       </c>
       <c r="G12">
         <v>325.1</v>
@@ -2527,28 +2527,28 @@
         <v>62.25</v>
       </c>
       <c r="M12">
-        <v>8.529987000000002</v>
+        <v>9.382985700000001</v>
       </c>
       <c r="N12">
-        <v>53.72001299999999</v>
+        <v>52.8670143</v>
       </c>
       <c r="O12">
-        <v>13.43000325</v>
+        <v>13.216753575</v>
       </c>
       <c r="P12">
-        <v>40.29000975</v>
+        <v>39.650260725</v>
       </c>
       <c r="Q12">
-        <v>41.79000975</v>
+        <v>41.150260725</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07057349106772053</v>
+        <v>0.07078760940019867</v>
       </c>
       <c r="T12">
-        <v>0.4828814517845491</v>
+        <v>0.4870550166227908</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.297783689471037</v>
+        <v>6.634348808610035</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06748072236617682</v>
+        <v>0.06746280277140515</v>
       </c>
       <c r="C13">
-        <v>1433.881712191616</v>
+        <v>1419.232843111515</v>
       </c>
       <c r="D13">
-        <v>1281.580712191616</v>
+        <v>1282.640843111516</v>
       </c>
       <c r="E13">
-        <v>-65.90100000000001</v>
+        <v>-50.19200000000001</v>
       </c>
       <c r="F13">
-        <v>172.799</v>
+        <v>188.508</v>
       </c>
       <c r="G13">
         <v>325.1</v>
@@ -2609,45 +2609,45 @@
         <v>62.25</v>
       </c>
       <c r="M13">
-        <v>9.382985700000001</v>
+        <v>10.4244924</v>
       </c>
       <c r="N13">
-        <v>52.8670143</v>
+        <v>51.8255076</v>
       </c>
       <c r="O13">
-        <v>13.216753575</v>
+        <v>12.9563769</v>
       </c>
       <c r="P13">
-        <v>39.650260725</v>
+        <v>38.8691307</v>
       </c>
       <c r="Q13">
-        <v>41.150260725</v>
+        <v>40.3691307</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07078760940019867</v>
+        <v>0.07100659405841495</v>
       </c>
       <c r="T13">
-        <v>0.4870550166227908</v>
+        <v>0.491323435207356</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.634348808610035</v>
+        <v>5.971513778455055</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06746280277140515</v>
+        <v>0.06736238317663348</v>
       </c>
       <c r="C14">
-        <v>1419.232843111515</v>
+        <v>1409.497314255579</v>
       </c>
       <c r="D14">
-        <v>1282.640843111516</v>
+        <v>1288.614314255579</v>
       </c>
       <c r="E14">
-        <v>-50.19200000000001</v>
+        <v>-34.483</v>
       </c>
       <c r="F14">
-        <v>188.508</v>
+        <v>204.217</v>
       </c>
       <c r="G14">
         <v>325.1</v>
@@ -2691,28 +2691,28 @@
         <v>62.25</v>
       </c>
       <c r="M14">
-        <v>10.4244924</v>
+        <v>11.2932001</v>
       </c>
       <c r="N14">
-        <v>51.8255076</v>
+        <v>50.9567999</v>
       </c>
       <c r="O14">
-        <v>12.9563769</v>
+        <v>12.739199975</v>
       </c>
       <c r="P14">
-        <v>38.8691307</v>
+        <v>38.217599925</v>
       </c>
       <c r="Q14">
-        <v>40.3691307</v>
+        <v>39.717599925</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07100659405841495</v>
+        <v>0.07123061284670516</v>
       </c>
       <c r="T14">
-        <v>0.491323435207356</v>
+        <v>0.4956899783570836</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.971513778455055</v>
+        <v>5.512166564727742</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06736238317663348</v>
+        <v>0.06726196358186183</v>
       </c>
       <c r="C15">
-        <v>1409.497314255579</v>
+        <v>1399.817684623342</v>
       </c>
       <c r="D15">
-        <v>1288.614314255579</v>
+        <v>1294.643684623342</v>
       </c>
       <c r="E15">
-        <v>-34.483</v>
+        <v>-18.77399999999997</v>
       </c>
       <c r="F15">
-        <v>204.217</v>
+        <v>219.926</v>
       </c>
       <c r="G15">
         <v>325.1</v>
@@ -2773,28 +2773,28 @@
         <v>62.25</v>
       </c>
       <c r="M15">
-        <v>11.2932001</v>
+        <v>12.1619078</v>
       </c>
       <c r="N15">
-        <v>50.9567999</v>
+        <v>50.0880922</v>
       </c>
       <c r="O15">
-        <v>12.739199975</v>
+        <v>12.52202305</v>
       </c>
       <c r="P15">
-        <v>38.217599925</v>
+        <v>37.56606915</v>
       </c>
       <c r="Q15">
-        <v>39.717599925</v>
+        <v>39.06606915</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07123061284670516</v>
+        <v>0.07145984137425794</v>
       </c>
       <c r="T15">
-        <v>0.4956899783570836</v>
+        <v>0.5001580690219213</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.512166564727742</v>
+        <v>5.118440381532903</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06726196358186183</v>
+        <v>0.06716154398709016</v>
       </c>
       <c r="C16">
-        <v>1399.817684623342</v>
+        <v>1390.194742553525</v>
       </c>
       <c r="D16">
-        <v>1294.643684623342</v>
+        <v>1300.729742553525</v>
       </c>
       <c r="E16">
-        <v>-18.77399999999997</v>
+        <v>-3.064999999999969</v>
       </c>
       <c r="F16">
-        <v>219.926</v>
+        <v>235.635</v>
       </c>
       <c r="G16">
         <v>325.1</v>
@@ -2855,28 +2855,28 @@
         <v>62.25</v>
       </c>
       <c r="M16">
-        <v>12.1619078</v>
+        <v>13.0306155</v>
       </c>
       <c r="N16">
-        <v>50.0880922</v>
+        <v>49.2193845</v>
       </c>
       <c r="O16">
-        <v>12.52202305</v>
+        <v>12.304846125</v>
       </c>
       <c r="P16">
-        <v>37.56606915</v>
+        <v>36.914538375</v>
       </c>
       <c r="Q16">
-        <v>39.06606915</v>
+        <v>38.414538375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07145984137425794</v>
+        <v>0.07169446351422372</v>
       </c>
       <c r="T16">
-        <v>0.5001580690219213</v>
+        <v>0.5047312912318138</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.118440381532903</v>
+        <v>4.777211022764043</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06716154398709016</v>
+        <v>0.06736112439231849</v>
       </c>
       <c r="C17">
-        <v>1390.194742553525</v>
+        <v>1362.445546300872</v>
       </c>
       <c r="D17">
-        <v>1300.729742553525</v>
+        <v>1288.689546300872</v>
       </c>
       <c r="E17">
-        <v>-3.065000000000026</v>
+        <v>12.64400000000001</v>
       </c>
       <c r="F17">
-        <v>235.635</v>
+        <v>251.344</v>
       </c>
       <c r="G17">
         <v>325.1</v>
@@ -2937,45 +2937,45 @@
         <v>62.25</v>
       </c>
       <c r="M17">
-        <v>13.0306155</v>
+        <v>14.5276832</v>
       </c>
       <c r="N17">
-        <v>49.2193845</v>
+        <v>47.7223168</v>
       </c>
       <c r="O17">
-        <v>12.304846125</v>
+        <v>11.9305792</v>
       </c>
       <c r="P17">
-        <v>36.91453837500001</v>
+        <v>35.7917376</v>
       </c>
       <c r="Q17">
-        <v>38.41453837500001</v>
+        <v>37.2917376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07169446351422372</v>
+        <v>0.07193467189561725</v>
       </c>
       <c r="T17">
-        <v>0.5047312912318138</v>
+        <v>0.509413399684799</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.777211022764044</v>
+        <v>4.284922732896598</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06736112439231849</v>
+        <v>0.06727945479754684</v>
       </c>
       <c r="C18">
-        <v>1362.445546300872</v>
+        <v>1351.636426396752</v>
       </c>
       <c r="D18">
-        <v>1288.689546300872</v>
+        <v>1293.589426396752</v>
       </c>
       <c r="E18">
-        <v>12.64400000000001</v>
+        <v>28.35300000000004</v>
       </c>
       <c r="F18">
-        <v>251.344</v>
+        <v>267.0530000000001</v>
       </c>
       <c r="G18">
         <v>325.1</v>
@@ -3019,28 +3019,28 @@
         <v>62.25</v>
       </c>
       <c r="M18">
-        <v>14.5276832</v>
+        <v>15.4356634</v>
       </c>
       <c r="N18">
-        <v>47.7223168</v>
+        <v>46.8143366</v>
       </c>
       <c r="O18">
-        <v>11.9305792</v>
+        <v>11.70358415</v>
       </c>
       <c r="P18">
-        <v>35.7917376</v>
+        <v>35.11075245</v>
       </c>
       <c r="Q18">
-        <v>37.2917376</v>
+        <v>36.61075245</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07193467189561725</v>
+        <v>0.07218066843077933</v>
       </c>
       <c r="T18">
-        <v>0.509413399684799</v>
+        <v>0.5142083300282179</v>
       </c>
       <c r="U18">
         <v>0.0578</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.284922732896598</v>
+        <v>4.032868454490915</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06727945479754684</v>
+        <v>0.06767028520277517</v>
       </c>
       <c r="C19">
-        <v>1351.636426396752</v>
+        <v>1312.810485989703</v>
       </c>
       <c r="D19">
-        <v>1293.589426396752</v>
+        <v>1270.472485989703</v>
       </c>
       <c r="E19">
-        <v>28.35300000000004</v>
+        <v>44.06200000000004</v>
       </c>
       <c r="F19">
-        <v>267.0530000000001</v>
+        <v>282.7620000000001</v>
       </c>
       <c r="G19">
         <v>325.1</v>
@@ -3101,45 +3101,45 @@
         <v>62.25</v>
       </c>
       <c r="M19">
-        <v>15.4356634</v>
+        <v>17.3333106</v>
       </c>
       <c r="N19">
-        <v>46.8143366</v>
+        <v>44.9166894</v>
       </c>
       <c r="O19">
-        <v>11.70358415</v>
+        <v>11.22917235</v>
       </c>
       <c r="P19">
-        <v>35.11075245</v>
+        <v>33.68751705</v>
       </c>
       <c r="Q19">
-        <v>36.61075245</v>
+        <v>35.18751705</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07218066843077933</v>
+        <v>0.07243266488143314</v>
       </c>
       <c r="T19">
-        <v>0.5142083300282179</v>
+        <v>0.5191202098922076</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.032868454490915</v>
+        <v>3.59135086404094</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06767028520277518</v>
+        <v>0.06801386560800352</v>
       </c>
       <c r="C20">
-        <v>1312.810485989702</v>
+        <v>1277.451171214658</v>
       </c>
       <c r="D20">
-        <v>1270.472485989702</v>
+        <v>1250.822171214658</v>
       </c>
       <c r="E20">
-        <v>44.06199999999998</v>
+        <v>59.77099999999999</v>
       </c>
       <c r="F20">
-        <v>282.762</v>
+        <v>298.471</v>
       </c>
       <c r="G20">
         <v>325.1</v>
@@ -3183,45 +3183,45 @@
         <v>62.25</v>
       </c>
       <c r="M20">
-        <v>17.3333106</v>
+        <v>19.1319911</v>
       </c>
       <c r="N20">
-        <v>44.9166894</v>
+        <v>43.1180089</v>
       </c>
       <c r="O20">
-        <v>11.22917235</v>
+        <v>10.779502225</v>
       </c>
       <c r="P20">
-        <v>33.68751705</v>
+        <v>32.338506675</v>
       </c>
       <c r="Q20">
-        <v>35.18751705</v>
+        <v>33.838506675</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07243266488143314</v>
+        <v>0.07269088346667101</v>
       </c>
       <c r="T20">
-        <v>0.5191202098922076</v>
+        <v>0.5241533707404936</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.59135086404094</v>
+        <v>3.253712573596169</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06801386560800352</v>
+        <v>0.06797944601323186</v>
       </c>
       <c r="C21">
-        <v>1277.451171214658</v>
+        <v>1263.683283370432</v>
       </c>
       <c r="D21">
-        <v>1250.822171214658</v>
+        <v>1252.763283370432</v>
       </c>
       <c r="E21">
-        <v>59.77099999999999</v>
+        <v>75.48000000000005</v>
       </c>
       <c r="F21">
-        <v>298.471</v>
+        <v>314.1800000000001</v>
       </c>
       <c r="G21">
         <v>325.1</v>
@@ -3265,28 +3265,28 @@
         <v>62.25</v>
       </c>
       <c r="M21">
-        <v>19.1319911</v>
+        <v>20.13893800000001</v>
       </c>
       <c r="N21">
-        <v>43.1180089</v>
+        <v>42.11106199999999</v>
       </c>
       <c r="O21">
-        <v>10.779502225</v>
+        <v>10.5277655</v>
       </c>
       <c r="P21">
-        <v>32.338506675</v>
+        <v>31.58329649999999</v>
       </c>
       <c r="Q21">
-        <v>33.838506675</v>
+        <v>33.08329649999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07269088346667101</v>
+        <v>0.07295555751653982</v>
       </c>
       <c r="T21">
-        <v>0.5241533707404936</v>
+        <v>0.5293123606099865</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.253712573596169</v>
+        <v>3.091026944916359</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06797944601323186</v>
+        <v>0.0691735264184602</v>
       </c>
       <c r="C22">
-        <v>1263.683283370432</v>
+        <v>1183.974523031286</v>
       </c>
       <c r="D22">
-        <v>1252.763283370432</v>
+        <v>1188.763523031286</v>
       </c>
       <c r="E22">
-        <v>75.48000000000005</v>
+        <v>91.18900000000005</v>
       </c>
       <c r="F22">
-        <v>314.1800000000001</v>
+        <v>329.8890000000001</v>
       </c>
       <c r="G22">
         <v>325.1</v>
@@ -3347,45 +3347,45 @@
         <v>62.25</v>
       </c>
       <c r="M22">
-        <v>20.13893800000001</v>
+        <v>23.71901910000001</v>
       </c>
       <c r="N22">
-        <v>42.11106199999999</v>
+        <v>38.53098089999999</v>
       </c>
       <c r="O22">
-        <v>10.5277655</v>
+        <v>9.632745224999997</v>
       </c>
       <c r="P22">
-        <v>31.58329649999999</v>
+        <v>28.89823567499999</v>
       </c>
       <c r="Q22">
-        <v>33.08329649999999</v>
+        <v>30.39823567499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07295555751653982</v>
+        <v>0.07322693217526606</v>
       </c>
       <c r="T22">
-        <v>0.5293123606099865</v>
+        <v>0.5346019578179478</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.091026944916359</v>
+        <v>2.624476152978855</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06917352641846018</v>
+        <v>0.06919760682368853</v>
       </c>
       <c r="C23">
-        <v>1183.974523031286</v>
+        <v>1167.042068531389</v>
       </c>
       <c r="D23">
-        <v>1188.763523031287</v>
+        <v>1187.540068531389</v>
       </c>
       <c r="E23">
-        <v>91.18899999999999</v>
+        <v>106.898</v>
       </c>
       <c r="F23">
-        <v>329.889</v>
+        <v>345.598</v>
       </c>
       <c r="G23">
         <v>325.1</v>
@@ -3429,28 +3429,28 @@
         <v>62.25</v>
       </c>
       <c r="M23">
-        <v>23.7190191</v>
+        <v>24.8484962</v>
       </c>
       <c r="N23">
-        <v>38.5309809</v>
+        <v>37.4015038</v>
       </c>
       <c r="O23">
-        <v>9.632745224999999</v>
+        <v>9.35037595</v>
       </c>
       <c r="P23">
-        <v>28.898235675</v>
+        <v>28.05112785</v>
       </c>
       <c r="Q23">
-        <v>30.398235675</v>
+        <v>29.55112785</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07322693217526606</v>
+        <v>0.07350526515857503</v>
       </c>
       <c r="T23">
-        <v>0.5346019578179478</v>
+        <v>0.540027185723549</v>
       </c>
       <c r="U23">
         <v>0.07190000000000001</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.624476152978855</v>
+        <v>2.505181782388908</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06919760682368853</v>
+        <v>0.06989443722891686</v>
       </c>
       <c r="C24">
-        <v>1167.042068531389</v>
+        <v>1116.988459470072</v>
       </c>
       <c r="D24">
-        <v>1187.540068531389</v>
+        <v>1153.195459470072</v>
       </c>
       <c r="E24">
-        <v>106.898</v>
+        <v>122.607</v>
       </c>
       <c r="F24">
-        <v>345.598</v>
+        <v>361.307</v>
       </c>
       <c r="G24">
         <v>325.1</v>
@@ -3511,45 +3511,45 @@
         <v>62.25</v>
       </c>
       <c r="M24">
-        <v>24.8484962</v>
+        <v>27.3870706</v>
       </c>
       <c r="N24">
-        <v>37.4015038</v>
+        <v>34.8629294</v>
       </c>
       <c r="O24">
-        <v>9.35037595</v>
+        <v>8.71573235</v>
       </c>
       <c r="P24">
-        <v>28.05112785</v>
+        <v>26.14719705</v>
       </c>
       <c r="Q24">
-        <v>29.55112785</v>
+        <v>27.64719705</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07350526515857503</v>
+        <v>0.07379082757002189</v>
       </c>
       <c r="T24">
-        <v>0.540027185723549</v>
+        <v>0.5455933286396855</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.505181782388908</v>
+        <v>2.272970370186288</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06989443722891686</v>
+        <v>0.0699477676341452</v>
       </c>
       <c r="C25">
-        <v>1116.988459470072</v>
+        <v>1098.732624412985</v>
       </c>
       <c r="D25">
-        <v>1153.195459470072</v>
+        <v>1150.648624412985</v>
       </c>
       <c r="E25">
-        <v>122.607</v>
+        <v>138.3160000000001</v>
       </c>
       <c r="F25">
-        <v>361.307</v>
+        <v>377.0160000000001</v>
       </c>
       <c r="G25">
         <v>325.1</v>
@@ -3593,28 +3593,28 @@
         <v>62.25</v>
       </c>
       <c r="M25">
-        <v>27.3870706</v>
+        <v>28.57781280000001</v>
       </c>
       <c r="N25">
-        <v>34.8629294</v>
+        <v>33.6721872</v>
       </c>
       <c r="O25">
-        <v>8.71573235</v>
+        <v>8.418046799999999</v>
       </c>
       <c r="P25">
-        <v>26.14719705</v>
+        <v>25.2541404</v>
       </c>
       <c r="Q25">
-        <v>27.64719705</v>
+        <v>26.7541404</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07379082757002189</v>
+        <v>0.07408390478177</v>
       </c>
       <c r="T25">
-        <v>0.5455933286396855</v>
+        <v>0.5513059490009833</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.272970370186288</v>
+        <v>2.178263271428525</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0699477676341452</v>
+        <v>0.07000109803937354</v>
       </c>
       <c r="C26">
-        <v>1098.732624412985</v>
+        <v>1080.488013949545</v>
       </c>
       <c r="D26">
-        <v>1150.648624412985</v>
+        <v>1148.113013949545</v>
       </c>
       <c r="E26">
-        <v>138.316</v>
+        <v>154.025</v>
       </c>
       <c r="F26">
-        <v>377.016</v>
+        <v>392.725</v>
       </c>
       <c r="G26">
         <v>325.1</v>
@@ -3675,28 +3675,28 @@
         <v>62.25</v>
       </c>
       <c r="M26">
-        <v>28.5778128</v>
+        <v>29.768555</v>
       </c>
       <c r="N26">
-        <v>33.6721872</v>
+        <v>32.48144499999999</v>
       </c>
       <c r="O26">
-        <v>8.418046799999999</v>
+        <v>8.120361249999998</v>
       </c>
       <c r="P26">
-        <v>25.2541404</v>
+        <v>24.36108375</v>
       </c>
       <c r="Q26">
-        <v>26.7541404</v>
+        <v>25.86108375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07408390478177</v>
+        <v>0.07438479738583138</v>
       </c>
       <c r="T26">
-        <v>0.5513059490009833</v>
+        <v>0.557170905905249</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.178263271428525</v>
+        <v>2.091132740571385</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07000109803937354</v>
+        <v>0.07005442844460189</v>
       </c>
       <c r="C27">
-        <v>1080.488013949545</v>
+        <v>1062.254554038164</v>
       </c>
       <c r="D27">
-        <v>1148.113013949545</v>
+        <v>1145.588554038163</v>
       </c>
       <c r="E27">
-        <v>154.025</v>
+        <v>169.734</v>
       </c>
       <c r="F27">
-        <v>392.725</v>
+        <v>408.434</v>
       </c>
       <c r="G27">
         <v>325.1</v>
@@ -3757,28 +3757,28 @@
         <v>62.25</v>
       </c>
       <c r="M27">
-        <v>29.768555</v>
+        <v>30.95929720000001</v>
       </c>
       <c r="N27">
-        <v>32.48144499999999</v>
+        <v>31.29070279999999</v>
       </c>
       <c r="O27">
-        <v>8.120361249999998</v>
+        <v>7.822675699999999</v>
       </c>
       <c r="P27">
-        <v>24.36108375</v>
+        <v>23.4680271</v>
       </c>
       <c r="Q27">
-        <v>25.86108375</v>
+        <v>24.9680271</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07438479738583138</v>
+        <v>0.07469382222243497</v>
       </c>
       <c r="T27">
-        <v>0.557170905905249</v>
+        <v>0.5631943751582787</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.091132740571385</v>
+        <v>2.010704558241716</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07005442844460189</v>
+        <v>0.0729832588498302</v>
       </c>
       <c r="C28">
-        <v>1062.254554038164</v>
+        <v>923.1153719733861</v>
       </c>
       <c r="D28">
-        <v>1145.588554038163</v>
+        <v>1022.158371973386</v>
       </c>
       <c r="E28">
-        <v>169.734</v>
+        <v>185.443</v>
       </c>
       <c r="F28">
-        <v>408.434</v>
+        <v>424.143</v>
       </c>
       <c r="G28">
         <v>325.1</v>
@@ -3839,45 +3839,45 @@
         <v>62.25</v>
       </c>
       <c r="M28">
-        <v>30.95929720000001</v>
+        <v>38.17287</v>
       </c>
       <c r="N28">
-        <v>31.29070279999999</v>
+        <v>24.07713</v>
       </c>
       <c r="O28">
-        <v>7.822675699999999</v>
+        <v>6.019282499999999</v>
       </c>
       <c r="P28">
-        <v>23.4680271</v>
+        <v>18.0578475</v>
       </c>
       <c r="Q28">
-        <v>24.9680271</v>
+        <v>19.5578475</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07469382222243497</v>
+        <v>0.07501131349291809</v>
       </c>
       <c r="T28">
-        <v>0.5631943751582787</v>
+        <v>0.569382870966186</v>
       </c>
       <c r="U28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.010704558241716</v>
+        <v>1.630739318264516</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0729832588498302</v>
+        <v>0.07314308925505855</v>
       </c>
       <c r="C29">
-        <v>923.1153719733861</v>
+        <v>901.4314806479724</v>
       </c>
       <c r="D29">
-        <v>1022.158371973386</v>
+        <v>1016.183480647972</v>
       </c>
       <c r="E29">
-        <v>185.443</v>
+        <v>201.1520000000001</v>
       </c>
       <c r="F29">
-        <v>424.143</v>
+        <v>439.8520000000001</v>
       </c>
       <c r="G29">
         <v>325.1</v>
@@ -3921,28 +3921,28 @@
         <v>62.25</v>
       </c>
       <c r="M29">
-        <v>38.17287</v>
+        <v>39.58668000000001</v>
       </c>
       <c r="N29">
-        <v>24.07713</v>
+        <v>22.66331999999999</v>
       </c>
       <c r="O29">
-        <v>6.019282499999999</v>
+        <v>5.665829999999998</v>
       </c>
       <c r="P29">
-        <v>18.0578475</v>
+        <v>16.99748999999999</v>
       </c>
       <c r="Q29">
-        <v>19.5578475</v>
+        <v>18.49748999999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07501131349291809</v>
+        <v>0.0753376239653591</v>
       </c>
       <c r="T29">
-        <v>0.569382870966186</v>
+        <v>0.5757432694354241</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.630739318264516</v>
+        <v>1.572498628326497</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07314308925505855</v>
+        <v>0.07330291966028687</v>
       </c>
       <c r="C30">
-        <v>901.4314806479724</v>
+        <v>879.8170342624812</v>
       </c>
       <c r="D30">
-        <v>1016.183480647972</v>
+        <v>1010.278034262481</v>
       </c>
       <c r="E30">
-        <v>201.1520000000001</v>
+        <v>216.8610000000001</v>
       </c>
       <c r="F30">
-        <v>439.8520000000001</v>
+        <v>455.5610000000001</v>
       </c>
       <c r="G30">
         <v>325.1</v>
@@ -4003,28 +4003,28 @@
         <v>62.25</v>
       </c>
       <c r="M30">
-        <v>39.58668000000001</v>
+        <v>41.00049000000001</v>
       </c>
       <c r="N30">
-        <v>22.66331999999999</v>
+        <v>21.24950999999999</v>
       </c>
       <c r="O30">
-        <v>5.665829999999998</v>
+        <v>5.312377499999998</v>
       </c>
       <c r="P30">
-        <v>16.99748999999999</v>
+        <v>15.9371325</v>
       </c>
       <c r="Q30">
-        <v>18.49748999999999</v>
+        <v>17.4371325</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0753376239653591</v>
+        <v>0.0756731262820942</v>
       </c>
       <c r="T30">
-        <v>0.5757432694354241</v>
+        <v>0.5822828340587251</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.572498628326497</v>
+        <v>1.518274537694549</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07330291966028687</v>
+        <v>0.08751786933230449</v>
       </c>
       <c r="C31">
-        <v>879.8170342624815</v>
+        <v>519.8658272266229</v>
       </c>
       <c r="D31">
-        <v>1010.278034262481</v>
+        <v>666.0358272266228</v>
       </c>
       <c r="E31">
-        <v>216.861</v>
+        <v>232.57</v>
       </c>
       <c r="F31">
-        <v>455.561</v>
+        <v>471.27</v>
       </c>
       <c r="G31">
         <v>325.1</v>
@@ -4085,45 +4085,45 @@
         <v>62.25</v>
       </c>
       <c r="M31">
-        <v>41.00049</v>
+        <v>69.18243600000001</v>
       </c>
       <c r="N31">
-        <v>21.24951</v>
+        <v>-6.93243600000001</v>
       </c>
       <c r="O31">
-        <v>5.3123775</v>
+        <v>-1.733109000000002</v>
       </c>
       <c r="P31">
-        <v>15.9371325</v>
+        <v>-5.199327000000007</v>
       </c>
       <c r="Q31">
-        <v>17.4371325</v>
+        <v>-3.699327000000007</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0756731262820942</v>
+        <v>0.0762637295582306</v>
       </c>
       <c r="T31">
-        <v>0.5822828340587251</v>
+        <v>0.5937947911999231</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.25</v>
+        <v>0.2249487138614199</v>
       </c>
       <c r="W31">
-        <v>0.0675</v>
+        <v>0.1137775288051436</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.51827453769455</v>
+        <v>0.8997948554456797</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08751786933230449</v>
+        <v>0.08852786933230447</v>
       </c>
       <c r="C32">
-        <v>519.8658272266229</v>
+        <v>488.4130937802587</v>
       </c>
       <c r="D32">
-        <v>666.0358272266228</v>
+        <v>650.2920937802587</v>
       </c>
       <c r="E32">
-        <v>232.57</v>
+        <v>248.279</v>
       </c>
       <c r="F32">
-        <v>471.27</v>
+        <v>486.979</v>
       </c>
       <c r="G32">
         <v>325.1</v>
@@ -4167,37 +4167,37 @@
         <v>62.25</v>
       </c>
       <c r="M32">
-        <v>69.18243600000001</v>
+        <v>71.48851720000002</v>
       </c>
       <c r="N32">
-        <v>-6.93243600000001</v>
+        <v>-9.238517200000018</v>
       </c>
       <c r="O32">
-        <v>-1.733109000000002</v>
+        <v>-2.309629300000005</v>
       </c>
       <c r="P32">
-        <v>-5.199327000000007</v>
+        <v>-6.928887900000014</v>
       </c>
       <c r="Q32">
-        <v>-3.699327000000007</v>
+        <v>-5.428887900000014</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0762637295582306</v>
+        <v>0.07670523288516147</v>
       </c>
       <c r="T32">
-        <v>0.5937947911999231</v>
+        <v>0.6024005128115161</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2249487138614199</v>
+        <v>0.217692303736858</v>
       </c>
       <c r="W32">
-        <v>0.1137775288051436</v>
+        <v>0.1148427698114293</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8997948554456797</v>
+        <v>0.870769214947432</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08852786933230447</v>
+        <v>0.08953786933230448</v>
       </c>
       <c r="C33">
-        <v>488.4130937802587</v>
+        <v>457.6874726063286</v>
       </c>
       <c r="D33">
-        <v>650.2920937802587</v>
+        <v>635.2754726063287</v>
       </c>
       <c r="E33">
-        <v>248.279</v>
+        <v>263.9880000000001</v>
       </c>
       <c r="F33">
-        <v>486.979</v>
+        <v>502.688</v>
       </c>
       <c r="G33">
         <v>325.1</v>
@@ -4249,37 +4249,37 @@
         <v>62.25</v>
       </c>
       <c r="M33">
-        <v>71.48851720000002</v>
+        <v>73.79459840000001</v>
       </c>
       <c r="N33">
-        <v>-9.238517200000018</v>
+        <v>-11.54459840000001</v>
       </c>
       <c r="O33">
-        <v>-2.309629300000005</v>
+        <v>-2.886149600000003</v>
       </c>
       <c r="P33">
-        <v>-6.928887900000014</v>
+        <v>-8.658448800000009</v>
       </c>
       <c r="Q33">
-        <v>-5.428887900000014</v>
+        <v>-7.158448800000009</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07670523288516147</v>
+        <v>0.0771597216040609</v>
       </c>
       <c r="T33">
-        <v>0.6024005128115161</v>
+        <v>0.6112593438822737</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.217692303736858</v>
+        <v>0.2108894192450812</v>
       </c>
       <c r="W33">
-        <v>0.1148427698114293</v>
+        <v>0.1158414332548221</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.870769214947432</v>
+        <v>0.8435576769803248</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08953786933230448</v>
+        <v>0.09054786933230448</v>
       </c>
       <c r="C34">
-        <v>457.6874726063286</v>
+        <v>427.6397289542552</v>
       </c>
       <c r="D34">
-        <v>635.2754726063287</v>
+        <v>620.9367289542553</v>
       </c>
       <c r="E34">
-        <v>263.9880000000001</v>
+        <v>279.697</v>
       </c>
       <c r="F34">
-        <v>502.688</v>
+        <v>518.397</v>
       </c>
       <c r="G34">
         <v>325.1</v>
@@ -4331,37 +4331,37 @@
         <v>62.25</v>
       </c>
       <c r="M34">
-        <v>73.79459840000001</v>
+        <v>76.10067960000002</v>
       </c>
       <c r="N34">
-        <v>-11.54459840000001</v>
+        <v>-13.85067960000002</v>
       </c>
       <c r="O34">
-        <v>-2.886149600000003</v>
+        <v>-3.462669900000005</v>
       </c>
       <c r="P34">
-        <v>-8.658448800000009</v>
+        <v>-10.38800970000002</v>
       </c>
       <c r="Q34">
-        <v>-7.158448800000009</v>
+        <v>-8.888009700000016</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0771597216040609</v>
+        <v>0.07762777715039017</v>
       </c>
       <c r="T34">
-        <v>0.6112593438822737</v>
+        <v>0.6203826176715613</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2108894192450812</v>
+        <v>0.204498830783109</v>
       </c>
       <c r="W34">
-        <v>0.1158414332548221</v>
+        <v>0.1167795716410396</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8435576769803248</v>
+        <v>0.8179953231324361</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09054786933230448</v>
+        <v>0.110332880635924</v>
       </c>
       <c r="C35">
-        <v>427.6397289542552</v>
+        <v>221.5589358445956</v>
       </c>
       <c r="D35">
-        <v>620.9367289542553</v>
+        <v>430.5649358445957</v>
       </c>
       <c r="E35">
-        <v>279.697</v>
+        <v>295.4060000000001</v>
       </c>
       <c r="F35">
-        <v>518.397</v>
+        <v>534.1060000000001</v>
       </c>
       <c r="G35">
         <v>325.1</v>
@@ -4413,45 +4413,45 @@
         <v>62.25</v>
       </c>
       <c r="M35">
-        <v>76.10067960000002</v>
+        <v>107.2484848</v>
       </c>
       <c r="N35">
-        <v>-13.85067960000002</v>
+        <v>-44.99848480000003</v>
       </c>
       <c r="O35">
-        <v>-3.462669900000005</v>
+        <v>-11.24962120000001</v>
       </c>
       <c r="P35">
-        <v>-10.38800970000002</v>
+        <v>-33.74886360000002</v>
       </c>
       <c r="Q35">
-        <v>-8.888009700000016</v>
+        <v>-32.24886360000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07762777715039017</v>
+        <v>0.07873882120360748</v>
       </c>
       <c r="T35">
-        <v>0.6203826176715613</v>
+        <v>0.6420389342539754</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.204498830783109</v>
+        <v>0.1451069451379326</v>
       </c>
       <c r="W35">
-        <v>0.1167795716410396</v>
+        <v>0.1716625254163031</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8179953231324361</v>
+        <v>0.5804277805517304</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.110332880635924</v>
+        <v>0.111882880635924</v>
       </c>
       <c r="C36">
-        <v>221.5589358445956</v>
+        <v>195.7508656446155</v>
       </c>
       <c r="D36">
-        <v>430.5649358445957</v>
+        <v>420.4658656446155</v>
       </c>
       <c r="E36">
-        <v>295.4060000000001</v>
+        <v>311.115</v>
       </c>
       <c r="F36">
-        <v>534.1060000000001</v>
+        <v>549.8150000000001</v>
       </c>
       <c r="G36">
         <v>325.1</v>
@@ -4495,37 +4495,37 @@
         <v>62.25</v>
       </c>
       <c r="M36">
-        <v>107.2484848</v>
+        <v>110.402852</v>
       </c>
       <c r="N36">
-        <v>-44.99848480000003</v>
+        <v>-48.15285200000001</v>
       </c>
       <c r="O36">
-        <v>-11.24962120000001</v>
+        <v>-12.038213</v>
       </c>
       <c r="P36">
-        <v>-33.74886360000002</v>
+        <v>-36.11463900000001</v>
       </c>
       <c r="Q36">
-        <v>-32.24886360000002</v>
+        <v>-34.61463900000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07873882120360748</v>
+        <v>0.07924557229904759</v>
       </c>
       <c r="T36">
-        <v>0.6420389342539754</v>
+        <v>0.6519164563194212</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1451069451379326</v>
+        <v>0.140961032419706</v>
       </c>
       <c r="W36">
-        <v>0.1716625254163031</v>
+        <v>0.1724950246901231</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5804277805517304</v>
+        <v>0.5638441296788238</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.111882880635924</v>
+        <v>0.113432880635924</v>
       </c>
       <c r="C37">
-        <v>195.7508656446155</v>
+        <v>170.405693332845</v>
       </c>
       <c r="D37">
-        <v>420.4658656446155</v>
+        <v>410.8296933328451</v>
       </c>
       <c r="E37">
-        <v>311.115</v>
+        <v>326.8240000000001</v>
       </c>
       <c r="F37">
-        <v>549.8150000000001</v>
+        <v>565.5240000000001</v>
       </c>
       <c r="G37">
         <v>325.1</v>
@@ -4577,37 +4577,37 @@
         <v>62.25</v>
       </c>
       <c r="M37">
-        <v>110.402852</v>
+        <v>113.5572192</v>
       </c>
       <c r="N37">
-        <v>-48.15285200000001</v>
+        <v>-51.30721920000002</v>
       </c>
       <c r="O37">
-        <v>-12.038213</v>
+        <v>-12.82680480000001</v>
       </c>
       <c r="P37">
-        <v>-36.11463900000001</v>
+        <v>-38.48041440000002</v>
       </c>
       <c r="Q37">
-        <v>-34.61463900000001</v>
+        <v>-36.98041440000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07924557229904759</v>
+        <v>0.07976815936622021</v>
       </c>
       <c r="T37">
-        <v>0.6519164563194212</v>
+        <v>0.6621026509494121</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.140961032419706</v>
+        <v>0.1370454481858252</v>
       </c>
       <c r="W37">
-        <v>0.1724950246901231</v>
+        <v>0.1732812740042863</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5638441296788238</v>
+        <v>0.5481817927433009</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.113432880635924</v>
+        <v>0.114982880635924</v>
       </c>
       <c r="C38">
-        <v>170.4056933328451</v>
+        <v>145.4923060796312</v>
       </c>
       <c r="D38">
-        <v>410.8296933328451</v>
+        <v>401.6253060796313</v>
       </c>
       <c r="E38">
-        <v>326.824</v>
+        <v>342.533</v>
       </c>
       <c r="F38">
-        <v>565.524</v>
+        <v>581.2330000000001</v>
       </c>
       <c r="G38">
         <v>325.1</v>
@@ -4659,37 +4659,37 @@
         <v>62.25</v>
       </c>
       <c r="M38">
-        <v>113.5572192</v>
+        <v>116.7115864</v>
       </c>
       <c r="N38">
-        <v>-51.30721920000001</v>
+        <v>-54.46158640000002</v>
       </c>
       <c r="O38">
-        <v>-12.8268048</v>
+        <v>-13.6153966</v>
       </c>
       <c r="P38">
-        <v>-38.4804144</v>
+        <v>-40.84618980000001</v>
       </c>
       <c r="Q38">
-        <v>-36.9804144</v>
+        <v>-39.34618980000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07976815936622021</v>
+        <v>0.08030733649901736</v>
       </c>
       <c r="T38">
-        <v>0.6621026509494121</v>
+        <v>0.6726122168374981</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1370454481858252</v>
+        <v>0.1333415171537759</v>
       </c>
       <c r="W38">
-        <v>0.1732812740042863</v>
+        <v>0.1740250233555218</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.548181792743301</v>
+        <v>0.5333660686151036</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.114982880635924</v>
+        <v>0.116532880635924</v>
       </c>
       <c r="C39">
-        <v>145.4923060796312</v>
+        <v>120.9823182105289</v>
       </c>
       <c r="D39">
-        <v>401.6253060796313</v>
+        <v>392.8243182105289</v>
       </c>
       <c r="E39">
-        <v>342.533</v>
+        <v>358.242</v>
       </c>
       <c r="F39">
-        <v>581.2330000000001</v>
+        <v>596.942</v>
       </c>
       <c r="G39">
         <v>325.1</v>
@@ -4741,37 +4741,37 @@
         <v>62.25</v>
       </c>
       <c r="M39">
-        <v>116.7115864</v>
+        <v>119.8659536</v>
       </c>
       <c r="N39">
-        <v>-54.46158640000002</v>
+        <v>-57.61595360000001</v>
       </c>
       <c r="O39">
-        <v>-13.6153966</v>
+        <v>-14.4039884</v>
       </c>
       <c r="P39">
-        <v>-40.84618980000001</v>
+        <v>-43.21196520000001</v>
       </c>
       <c r="Q39">
-        <v>-39.34618980000001</v>
+        <v>-41.71196520000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08030733649901736</v>
+        <v>0.0808639064425499</v>
       </c>
       <c r="T39">
-        <v>0.6726122168374981</v>
+        <v>0.6834608009800383</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1333415171537759</v>
+        <v>0.1298325298602555</v>
       </c>
       <c r="W39">
-        <v>0.1740250233555218</v>
+        <v>0.1747296280040607</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5333660686151036</v>
+        <v>0.5193301194410219</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.116532880635924</v>
+        <v>0.118082880635924</v>
       </c>
       <c r="C40">
-        <v>120.9823182105289</v>
+        <v>96.84977880715189</v>
       </c>
       <c r="D40">
-        <v>392.8243182105289</v>
+        <v>384.4007788071519</v>
       </c>
       <c r="E40">
-        <v>358.242</v>
+        <v>373.951</v>
       </c>
       <c r="F40">
-        <v>596.942</v>
+        <v>612.6510000000001</v>
       </c>
       <c r="G40">
         <v>325.1</v>
@@ -4823,37 +4823,37 @@
         <v>62.25</v>
       </c>
       <c r="M40">
-        <v>119.8659536</v>
+        <v>123.0203208</v>
       </c>
       <c r="N40">
-        <v>-57.61595360000001</v>
+        <v>-60.77032080000002</v>
       </c>
       <c r="O40">
-        <v>-14.4039884</v>
+        <v>-15.19258020000001</v>
       </c>
       <c r="P40">
-        <v>-43.21196520000001</v>
+        <v>-45.57774060000001</v>
       </c>
       <c r="Q40">
-        <v>-41.71196520000001</v>
+        <v>-44.07774060000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0808639064425499</v>
+        <v>0.08143872458095235</v>
       </c>
       <c r="T40">
-        <v>0.6834608009800383</v>
+        <v>0.6946650764059406</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1298325298602555</v>
+        <v>0.1265034906330694</v>
       </c>
       <c r="W40">
-        <v>0.1747296280040607</v>
+        <v>0.1753980990808797</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5193301194410219</v>
+        <v>0.5060139625322777</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.118082880635924</v>
+        <v>0.1338003427097151</v>
       </c>
       <c r="C41">
-        <v>96.84977880715189</v>
+        <v>12.48417502587813</v>
       </c>
       <c r="D41">
-        <v>384.4007788071519</v>
+        <v>315.7441750258783</v>
       </c>
       <c r="E41">
-        <v>373.951</v>
+        <v>389.6600000000001</v>
       </c>
       <c r="F41">
-        <v>612.6510000000001</v>
+        <v>628.3600000000001</v>
       </c>
       <c r="G41">
         <v>325.1</v>
@@ -4905,45 +4905,45 @@
         <v>62.25</v>
       </c>
       <c r="M41">
-        <v>123.0203208</v>
+        <v>148.167288</v>
       </c>
       <c r="N41">
-        <v>-60.77032080000002</v>
+        <v>-85.91728800000004</v>
       </c>
       <c r="O41">
-        <v>-15.19258020000001</v>
+        <v>-21.47932200000001</v>
       </c>
       <c r="P41">
-        <v>-45.57774060000001</v>
+        <v>-64.43796600000003</v>
       </c>
       <c r="Q41">
-        <v>-44.07774060000001</v>
+        <v>-62.93796600000003</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08143872458095235</v>
+        <v>0.08231180678028675</v>
       </c>
       <c r="T41">
-        <v>0.6946650764059406</v>
+        <v>0.7116830735380112</v>
       </c>
       <c r="U41">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1265034906330694</v>
+        <v>0.1050333053271515</v>
       </c>
       <c r="W41">
-        <v>0.1753980990808797</v>
+        <v>0.2110331466038577</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5060139625322777</v>
+        <v>0.4201332213086061</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1338003427097151</v>
+        <v>0.1357003427097151</v>
       </c>
       <c r="C42">
-        <v>12.48417502587813</v>
+        <v>-9.897924480385768</v>
       </c>
       <c r="D42">
-        <v>315.7441750258783</v>
+        <v>309.0710755196143</v>
       </c>
       <c r="E42">
-        <v>389.6600000000001</v>
+        <v>405.369</v>
       </c>
       <c r="F42">
-        <v>628.3600000000001</v>
+        <v>644.0690000000001</v>
       </c>
       <c r="G42">
         <v>325.1</v>
@@ -4987,37 +4987,37 @@
         <v>62.25</v>
       </c>
       <c r="M42">
-        <v>148.167288</v>
+        <v>151.8714702</v>
       </c>
       <c r="N42">
-        <v>-85.91728800000004</v>
+        <v>-89.62147020000003</v>
       </c>
       <c r="O42">
-        <v>-21.47932200000001</v>
+        <v>-22.40536755000001</v>
       </c>
       <c r="P42">
-        <v>-64.43796600000003</v>
+        <v>-67.21610265000002</v>
       </c>
       <c r="Q42">
-        <v>-62.93796600000003</v>
+        <v>-65.71610265000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08231180678028675</v>
+        <v>0.08293065096300348</v>
       </c>
       <c r="T42">
-        <v>0.7116830735380112</v>
+        <v>0.7237454985132317</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1050333053271515</v>
+        <v>0.102471517392343</v>
       </c>
       <c r="W42">
-        <v>0.2110331466038577</v>
+        <v>0.2116372161988855</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4201332213086061</v>
+        <v>0.4098860695693719</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1357003427097151</v>
+        <v>0.1376003427097151</v>
       </c>
       <c r="C43">
-        <v>-9.897924480385768</v>
+        <v>-32.00379649800107</v>
       </c>
       <c r="D43">
-        <v>309.0710755196143</v>
+        <v>302.674203501999</v>
       </c>
       <c r="E43">
-        <v>405.369</v>
+        <v>421.0780000000001</v>
       </c>
       <c r="F43">
-        <v>644.0690000000001</v>
+        <v>659.7780000000001</v>
       </c>
       <c r="G43">
         <v>325.1</v>
@@ -5069,37 +5069,37 @@
         <v>62.25</v>
       </c>
       <c r="M43">
-        <v>151.8714702</v>
+        <v>155.5756524</v>
       </c>
       <c r="N43">
-        <v>-89.62147020000003</v>
+        <v>-93.32565240000002</v>
       </c>
       <c r="O43">
-        <v>-22.40536755000001</v>
+        <v>-23.33141310000001</v>
       </c>
       <c r="P43">
-        <v>-67.21610265000002</v>
+        <v>-69.99423930000002</v>
       </c>
       <c r="Q43">
-        <v>-65.71610265000002</v>
+        <v>-68.49423930000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08293065096300348</v>
+        <v>0.08357083460029664</v>
       </c>
       <c r="T43">
-        <v>0.7237454985132317</v>
+        <v>0.7362238691772529</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.102471517392343</v>
+        <v>0.1000317193591919</v>
       </c>
       <c r="W43">
-        <v>0.2116372161988855</v>
+        <v>0.2122125205751025</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4098860695693719</v>
+        <v>0.4001268774367678</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1376003427097151</v>
+        <v>0.1395003427097151</v>
       </c>
       <c r="C44">
-        <v>-32.00379649800095</v>
+        <v>-53.8502445587344</v>
       </c>
       <c r="D44">
-        <v>302.674203501999</v>
+        <v>296.5367554412657</v>
       </c>
       <c r="E44">
-        <v>421.078</v>
+        <v>436.787</v>
       </c>
       <c r="F44">
-        <v>659.778</v>
+        <v>675.4870000000001</v>
       </c>
       <c r="G44">
         <v>325.1</v>
@@ -5151,37 +5151,37 @@
         <v>62.25</v>
       </c>
       <c r="M44">
-        <v>155.5756524</v>
+        <v>159.2798346</v>
       </c>
       <c r="N44">
-        <v>-93.32565240000002</v>
+        <v>-97.02983460000002</v>
       </c>
       <c r="O44">
-        <v>-23.33141310000001</v>
+        <v>-24.25745865</v>
       </c>
       <c r="P44">
-        <v>-69.99423930000002</v>
+        <v>-72.77237595000001</v>
       </c>
       <c r="Q44">
-        <v>-68.49423930000002</v>
+        <v>-71.27237595000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08357083460029664</v>
+        <v>0.08423348082135447</v>
       </c>
       <c r="T44">
-        <v>0.7362238691772529</v>
+        <v>0.7491400774084327</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1000317193591919</v>
+        <v>0.09770540030432703</v>
       </c>
       <c r="W44">
-        <v>0.2122125205751025</v>
+        <v>0.2127610666082397</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4001268774367678</v>
+        <v>0.3908216012173081</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1395003427097151</v>
+        <v>0.1414003427097151</v>
       </c>
       <c r="C45">
-        <v>-53.8502445587344</v>
+        <v>-75.45273635352009</v>
       </c>
       <c r="D45">
-        <v>296.5367554412657</v>
+        <v>290.6432636464799</v>
       </c>
       <c r="E45">
-        <v>436.787</v>
+        <v>452.496</v>
       </c>
       <c r="F45">
-        <v>675.4870000000001</v>
+        <v>691.196</v>
       </c>
       <c r="G45">
         <v>325.1</v>
@@ -5233,37 +5233,37 @@
         <v>62.25</v>
       </c>
       <c r="M45">
-        <v>159.2798346</v>
+        <v>162.9840168</v>
       </c>
       <c r="N45">
-        <v>-97.02983460000002</v>
+        <v>-100.7340168</v>
       </c>
       <c r="O45">
-        <v>-24.25745865</v>
+        <v>-25.1835042</v>
       </c>
       <c r="P45">
-        <v>-72.77237595000001</v>
+        <v>-75.5505126</v>
       </c>
       <c r="Q45">
-        <v>-71.27237595000001</v>
+        <v>-74.0505126</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08423348082135447</v>
+        <v>0.08491979297887867</v>
       </c>
       <c r="T45">
-        <v>0.7491400774084327</v>
+        <v>0.7625175787907263</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.09770540030432703</v>
+        <v>0.09548482302468324</v>
       </c>
       <c r="W45">
-        <v>0.2127610666082397</v>
+        <v>0.2132846787307797</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3908216012173081</v>
+        <v>0.3819392920987329</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1414003427097151</v>
+        <v>0.1433003427097151</v>
       </c>
       <c r="C46">
-        <v>-75.45273635352009</v>
+        <v>-96.82553389085206</v>
       </c>
       <c r="D46">
-        <v>290.6432636464799</v>
+        <v>284.979466109148</v>
       </c>
       <c r="E46">
-        <v>452.496</v>
+        <v>468.205</v>
       </c>
       <c r="F46">
-        <v>691.196</v>
+        <v>706.9050000000001</v>
       </c>
       <c r="G46">
         <v>325.1</v>
@@ -5315,37 +5315,37 @@
         <v>62.25</v>
       </c>
       <c r="M46">
-        <v>162.9840168</v>
+        <v>166.688199</v>
       </c>
       <c r="N46">
-        <v>-100.7340168</v>
+        <v>-104.438199</v>
       </c>
       <c r="O46">
-        <v>-25.1835042</v>
+        <v>-26.10954975000001</v>
       </c>
       <c r="P46">
-        <v>-75.5505126</v>
+        <v>-78.32864925000001</v>
       </c>
       <c r="Q46">
-        <v>-74.0505126</v>
+        <v>-76.82864925000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08491979297887867</v>
+        <v>0.08563106194213099</v>
       </c>
       <c r="T46">
-        <v>0.7625175787907263</v>
+        <v>0.7763815347687394</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09548482302468324</v>
+        <v>0.09336293806857915</v>
       </c>
       <c r="W46">
-        <v>0.2132846787307797</v>
+        <v>0.213785019203429</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3819392920987329</v>
+        <v>0.3734517522743166</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1433003427097151</v>
+        <v>0.1452003427097151</v>
       </c>
       <c r="C47">
-        <v>-96.82553389085206</v>
+        <v>-117.9818087276063</v>
       </c>
       <c r="D47">
-        <v>284.979466109148</v>
+        <v>279.5321912723937</v>
       </c>
       <c r="E47">
-        <v>468.205</v>
+        <v>483.914</v>
       </c>
       <c r="F47">
-        <v>706.9050000000001</v>
+        <v>722.614</v>
       </c>
       <c r="G47">
         <v>325.1</v>
@@ -5397,37 +5397,37 @@
         <v>62.25</v>
       </c>
       <c r="M47">
-        <v>166.688199</v>
+        <v>170.3923812</v>
       </c>
       <c r="N47">
-        <v>-104.438199</v>
+        <v>-108.1423812</v>
       </c>
       <c r="O47">
-        <v>-26.10954975000001</v>
+        <v>-27.0355953</v>
       </c>
       <c r="P47">
-        <v>-78.32864925000001</v>
+        <v>-81.10678590000001</v>
       </c>
       <c r="Q47">
-        <v>-76.82864925000001</v>
+        <v>-79.60678590000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08563106194213099</v>
+        <v>0.08636867420031862</v>
       </c>
       <c r="T47">
-        <v>0.7763815347687394</v>
+        <v>0.7907589705977902</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09336293806857915</v>
+        <v>0.09133330898013178</v>
       </c>
       <c r="W47">
-        <v>0.213785019203429</v>
+        <v>0.2142636057424849</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3734517522743166</v>
+        <v>0.3653332359205271</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1452003427097151</v>
+        <v>0.1471003427097151</v>
       </c>
       <c r="C48">
-        <v>-117.9818087276063</v>
+        <v>-138.9337442321731</v>
       </c>
       <c r="D48">
-        <v>279.5321912723937</v>
+        <v>274.2892557678269</v>
       </c>
       <c r="E48">
-        <v>483.914</v>
+        <v>499.623</v>
       </c>
       <c r="F48">
-        <v>722.614</v>
+        <v>738.3230000000001</v>
       </c>
       <c r="G48">
         <v>325.1</v>
@@ -5479,37 +5479,37 @@
         <v>62.25</v>
       </c>
       <c r="M48">
-        <v>170.3923812</v>
+        <v>174.0965634</v>
       </c>
       <c r="N48">
-        <v>-108.1423812</v>
+        <v>-111.8465634</v>
       </c>
       <c r="O48">
-        <v>-27.0355953</v>
+        <v>-27.96164085000001</v>
       </c>
       <c r="P48">
-        <v>-81.10678590000001</v>
+        <v>-83.88492255000003</v>
       </c>
       <c r="Q48">
-        <v>-79.60678590000001</v>
+        <v>-82.38492255000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08636867420031862</v>
+        <v>0.08713412088334349</v>
       </c>
       <c r="T48">
-        <v>0.7907589705977902</v>
+        <v>0.8056789511751069</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09133330898013178</v>
+        <v>0.08939004708693749</v>
       </c>
       <c r="W48">
-        <v>0.2142636057424849</v>
+        <v>0.2147218268969001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3653332359205271</v>
+        <v>0.3575601883477499</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1471003427097151</v>
+        <v>0.1490003427097151</v>
       </c>
       <c r="C49">
-        <v>-138.9337442321731</v>
+        <v>-159.6926265511185</v>
       </c>
       <c r="D49">
-        <v>274.2892557678269</v>
+        <v>269.2393734488817</v>
       </c>
       <c r="E49">
-        <v>499.623</v>
+        <v>515.3320000000001</v>
       </c>
       <c r="F49">
-        <v>738.3230000000001</v>
+        <v>754.0320000000002</v>
       </c>
       <c r="G49">
         <v>325.1</v>
@@ -5561,37 +5561,37 @@
         <v>62.25</v>
       </c>
       <c r="M49">
-        <v>174.0965634</v>
+        <v>177.8007456000001</v>
       </c>
       <c r="N49">
-        <v>-111.8465634</v>
+        <v>-115.5507456000001</v>
       </c>
       <c r="O49">
-        <v>-27.96164085000001</v>
+        <v>-28.88768640000001</v>
       </c>
       <c r="P49">
-        <v>-83.88492255000003</v>
+        <v>-86.66305920000005</v>
       </c>
       <c r="Q49">
-        <v>-82.38492255000003</v>
+        <v>-85.16305920000005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08713412088334349</v>
+        <v>0.08792900782340779</v>
       </c>
       <c r="T49">
-        <v>0.8056789511751069</v>
+        <v>0.8211727771592436</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08939004708693749</v>
+        <v>0.08752775443929295</v>
       </c>
       <c r="W49">
-        <v>0.2147218268969001</v>
+        <v>0.2151609555032147</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3575601883477499</v>
+        <v>0.3501110177571718</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1490003427097151</v>
+        <v>0.1509003427097151</v>
       </c>
       <c r="C50">
-        <v>-159.6926265511183</v>
+        <v>-180.2689257088933</v>
       </c>
       <c r="D50">
-        <v>269.2393734488817</v>
+        <v>264.3720742911066</v>
       </c>
       <c r="E50">
-        <v>515.332</v>
+        <v>531.0409999999999</v>
       </c>
       <c r="F50">
-        <v>754.032</v>
+        <v>769.741</v>
       </c>
       <c r="G50">
         <v>325.1</v>
@@ -5643,37 +5643,37 @@
         <v>62.25</v>
       </c>
       <c r="M50">
-        <v>177.8007456</v>
+        <v>181.5049278</v>
       </c>
       <c r="N50">
-        <v>-115.5507456</v>
+        <v>-119.2549278</v>
       </c>
       <c r="O50">
-        <v>-28.88768640000001</v>
+        <v>-29.81373195</v>
       </c>
       <c r="P50">
-        <v>-86.66305920000002</v>
+        <v>-89.44119584999999</v>
       </c>
       <c r="Q50">
-        <v>-85.16305920000002</v>
+        <v>-87.94119584999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08792900782340779</v>
+        <v>0.08875506680033735</v>
       </c>
       <c r="T50">
-        <v>0.8211727771592436</v>
+        <v>0.837274204162366</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08752775443929296</v>
+        <v>0.08574147373645026</v>
       </c>
       <c r="W50">
-        <v>0.2151609555032147</v>
+        <v>0.215582160492945</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3501110177571718</v>
+        <v>0.3429658949458011</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1509003427097151</v>
+        <v>0.1528003427097151</v>
       </c>
       <c r="C51">
-        <v>-180.2689257088933</v>
+        <v>-200.6723680670437</v>
       </c>
       <c r="D51">
-        <v>264.3720742911066</v>
+        <v>259.6776319329563</v>
       </c>
       <c r="E51">
-        <v>531.0409999999999</v>
+        <v>546.75</v>
       </c>
       <c r="F51">
-        <v>769.741</v>
+        <v>785.45</v>
       </c>
       <c r="G51">
         <v>325.1</v>
@@ -5725,37 +5725,37 @@
         <v>62.25</v>
       </c>
       <c r="M51">
-        <v>181.5049278</v>
+        <v>185.20911</v>
       </c>
       <c r="N51">
-        <v>-119.2549278</v>
+        <v>-122.95911</v>
       </c>
       <c r="O51">
-        <v>-29.81373195</v>
+        <v>-30.7397775</v>
       </c>
       <c r="P51">
-        <v>-89.44119584999999</v>
+        <v>-92.21933250000001</v>
       </c>
       <c r="Q51">
-        <v>-87.94119584999999</v>
+        <v>-90.71933250000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08875506680033735</v>
+        <v>0.0896141681363441</v>
       </c>
       <c r="T51">
-        <v>0.837274204162366</v>
+        <v>0.8540196882456134</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08574147373645026</v>
+        <v>0.08402664426172125</v>
       </c>
       <c r="W51">
-        <v>0.215582160492945</v>
+        <v>0.2159865172830861</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3429658949458011</v>
+        <v>0.336106577046885</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1528003427097151</v>
+        <v>0.1547003427097151</v>
       </c>
       <c r="C52">
-        <v>-200.6723680670437</v>
+        <v>-220.9120011981792</v>
       </c>
       <c r="D52">
-        <v>259.6776319329563</v>
+        <v>255.146998801821</v>
       </c>
       <c r="E52">
-        <v>546.75</v>
+        <v>562.4590000000001</v>
       </c>
       <c r="F52">
-        <v>785.45</v>
+        <v>801.1590000000001</v>
       </c>
       <c r="G52">
         <v>325.1</v>
@@ -5807,37 +5807,37 @@
         <v>62.25</v>
       </c>
       <c r="M52">
-        <v>185.20911</v>
+        <v>188.9132922</v>
       </c>
       <c r="N52">
-        <v>-122.95911</v>
+        <v>-126.6632922</v>
       </c>
       <c r="O52">
-        <v>-30.7397775</v>
+        <v>-31.66582305000001</v>
       </c>
       <c r="P52">
-        <v>-92.21933250000001</v>
+        <v>-94.99746915000003</v>
       </c>
       <c r="Q52">
-        <v>-90.71933250000001</v>
+        <v>-93.49746915000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0896141681363441</v>
+        <v>0.09050833483300419</v>
       </c>
       <c r="T52">
-        <v>0.8540196882456134</v>
+        <v>0.8714486614751158</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08402664426172125</v>
+        <v>0.08237906300168749</v>
       </c>
       <c r="W52">
-        <v>0.2159865172830861</v>
+        <v>0.2163750169442021</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.336106577046885</v>
+        <v>0.3295162520067499</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1547003427097151</v>
+        <v>0.1566003427097151</v>
       </c>
       <c r="C53">
-        <v>-220.9120011981792</v>
+        <v>-240.9962520852051</v>
       </c>
       <c r="D53">
-        <v>255.146998801821</v>
+        <v>250.7717479147949</v>
       </c>
       <c r="E53">
-        <v>562.4590000000001</v>
+        <v>578.168</v>
       </c>
       <c r="F53">
-        <v>801.1590000000001</v>
+        <v>816.8680000000001</v>
       </c>
       <c r="G53">
         <v>325.1</v>
@@ -5889,37 +5889,37 @@
         <v>62.25</v>
       </c>
       <c r="M53">
-        <v>188.9132922</v>
+        <v>192.6174744</v>
       </c>
       <c r="N53">
-        <v>-126.6632922</v>
+        <v>-130.3674744</v>
       </c>
       <c r="O53">
-        <v>-31.66582305000001</v>
+        <v>-32.59186860000001</v>
       </c>
       <c r="P53">
-        <v>-94.99746915000003</v>
+        <v>-97.77560580000002</v>
       </c>
       <c r="Q53">
-        <v>-93.49746915000003</v>
+        <v>-96.27560580000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09050833483300419</v>
+        <v>0.09143975847535846</v>
       </c>
       <c r="T53">
-        <v>0.8714486614751158</v>
+        <v>0.8896038419225141</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08237906300168749</v>
+        <v>0.08079485025165505</v>
       </c>
       <c r="W53">
-        <v>0.2163750169442021</v>
+        <v>0.2167485743106597</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3295162520067499</v>
+        <v>0.3231794010066201</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1566003427097151</v>
+        <v>0.1585003427097151</v>
       </c>
       <c r="C54">
-        <v>-240.9962520852051</v>
+        <v>-260.9329794335182</v>
       </c>
       <c r="D54">
-        <v>250.7717479147949</v>
+        <v>246.5440205664819</v>
       </c>
       <c r="E54">
-        <v>578.168</v>
+        <v>593.8770000000001</v>
       </c>
       <c r="F54">
-        <v>816.8680000000001</v>
+        <v>832.5770000000001</v>
       </c>
       <c r="G54">
         <v>325.1</v>
@@ -5971,37 +5971,37 @@
         <v>62.25</v>
       </c>
       <c r="M54">
-        <v>192.6174744</v>
+        <v>196.3216566</v>
       </c>
       <c r="N54">
-        <v>-130.3674744</v>
+        <v>-134.0716566</v>
       </c>
       <c r="O54">
-        <v>-32.59186860000001</v>
+        <v>-33.51791415000001</v>
       </c>
       <c r="P54">
-        <v>-97.77560580000002</v>
+        <v>-100.55374245</v>
       </c>
       <c r="Q54">
-        <v>-96.27560580000002</v>
+        <v>-99.05374245000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09143975847535846</v>
+        <v>0.09241081716632352</v>
       </c>
       <c r="T54">
-        <v>0.8896038419225141</v>
+        <v>0.9085315832400144</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08079485025165505</v>
+        <v>0.07927041911483135</v>
       </c>
       <c r="W54">
-        <v>0.2167485743106597</v>
+        <v>0.2171080351727228</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3231794010066201</v>
+        <v>0.3170816764593254</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1585003427097151</v>
+        <v>0.1604003427097151</v>
       </c>
       <c r="C55">
-        <v>-260.9329794335182</v>
+        <v>-280.7295207793834</v>
       </c>
       <c r="D55">
-        <v>246.5440205664819</v>
+        <v>242.4564792206166</v>
       </c>
       <c r="E55">
-        <v>593.8770000000001</v>
+        <v>609.586</v>
       </c>
       <c r="F55">
-        <v>832.5770000000001</v>
+        <v>848.2860000000001</v>
       </c>
       <c r="G55">
         <v>325.1</v>
@@ -6053,37 +6053,37 @@
         <v>62.25</v>
       </c>
       <c r="M55">
-        <v>196.3216566</v>
+        <v>200.0258388</v>
       </c>
       <c r="N55">
-        <v>-134.0716566</v>
+        <v>-137.7758388</v>
       </c>
       <c r="O55">
-        <v>-33.51791415000001</v>
+        <v>-34.44395970000001</v>
       </c>
       <c r="P55">
-        <v>-100.55374245</v>
+        <v>-103.3318791</v>
       </c>
       <c r="Q55">
-        <v>-99.05374245000003</v>
+        <v>-101.8318791</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09241081716632352</v>
+        <v>0.09342409580037403</v>
       </c>
       <c r="T55">
-        <v>0.9085315832400144</v>
+        <v>0.9282822698321884</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07927041911483135</v>
+        <v>0.07780244839048263</v>
       </c>
       <c r="W55">
-        <v>0.2171080351727228</v>
+        <v>0.2174541826695242</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3170816764593254</v>
+        <v>0.3112097935619305</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1604003427097151</v>
+        <v>0.1623003427097151</v>
       </c>
       <c r="C56">
-        <v>-280.7295207793834</v>
+        <v>-300.3927349885813</v>
       </c>
       <c r="D56">
-        <v>242.4564792206166</v>
+        <v>238.5022650114188</v>
       </c>
       <c r="E56">
-        <v>609.586</v>
+        <v>625.2950000000001</v>
       </c>
       <c r="F56">
-        <v>848.2860000000001</v>
+        <v>863.9950000000001</v>
       </c>
       <c r="G56">
         <v>325.1</v>
@@ -6135,37 +6135,37 @@
         <v>62.25</v>
       </c>
       <c r="M56">
-        <v>200.0258388</v>
+        <v>203.730021</v>
       </c>
       <c r="N56">
-        <v>-137.7758388</v>
+        <v>-141.480021</v>
       </c>
       <c r="O56">
-        <v>-34.44395970000001</v>
+        <v>-35.37000525000001</v>
       </c>
       <c r="P56">
-        <v>-103.3318791</v>
+        <v>-106.11001575</v>
       </c>
       <c r="Q56">
-        <v>-101.8318791</v>
+        <v>-104.61001575</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09342409580037403</v>
+        <v>0.09448240904038234</v>
       </c>
       <c r="T56">
-        <v>0.9282822698321884</v>
+        <v>0.9489107647173483</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07780244839048263</v>
+        <v>0.07638785841974659</v>
       </c>
       <c r="W56">
-        <v>0.2174541826695242</v>
+        <v>0.2177877429846238</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3112097935619305</v>
+        <v>0.3055514336789863</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1623003427097151</v>
+        <v>0.1642003427097151</v>
       </c>
       <c r="C57">
-        <v>-300.3927349885813</v>
+        <v>-319.9290406631327</v>
       </c>
       <c r="D57">
-        <v>238.5022650114188</v>
+        <v>234.6749593368675</v>
       </c>
       <c r="E57">
-        <v>625.2950000000001</v>
+        <v>641.0040000000001</v>
       </c>
       <c r="F57">
-        <v>863.9950000000001</v>
+        <v>879.7040000000002</v>
       </c>
       <c r="G57">
         <v>325.1</v>
@@ -6217,37 +6217,37 @@
         <v>62.25</v>
       </c>
       <c r="M57">
-        <v>203.730021</v>
+        <v>207.4342032</v>
       </c>
       <c r="N57">
-        <v>-141.480021</v>
+        <v>-145.1842032</v>
       </c>
       <c r="O57">
-        <v>-35.37000525000001</v>
+        <v>-36.29605080000001</v>
       </c>
       <c r="P57">
-        <v>-106.11001575</v>
+        <v>-108.8881524</v>
       </c>
       <c r="Q57">
-        <v>-104.61001575</v>
+        <v>-107.3881524</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09448240904038234</v>
+        <v>0.09558882742766375</v>
       </c>
       <c r="T57">
-        <v>0.9489107647173483</v>
+        <v>0.9704769184609243</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07638785841974659</v>
+        <v>0.07502378951939397</v>
       </c>
       <c r="W57">
-        <v>0.2177877429846238</v>
+        <v>0.2181093904313269</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3055514336789863</v>
+        <v>0.3000951580775758</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1642003427097151</v>
+        <v>0.1661003427097151</v>
       </c>
       <c r="C58">
-        <v>-319.9290406631327</v>
+        <v>-339.3444509084962</v>
       </c>
       <c r="D58">
-        <v>234.6749593368675</v>
+        <v>230.9685490915039</v>
       </c>
       <c r="E58">
-        <v>641.0040000000001</v>
+        <v>656.7130000000001</v>
       </c>
       <c r="F58">
-        <v>879.7040000000002</v>
+        <v>895.4130000000001</v>
       </c>
       <c r="G58">
         <v>325.1</v>
@@ -6299,37 +6299,37 @@
         <v>62.25</v>
       </c>
       <c r="M58">
-        <v>207.4342032</v>
+        <v>211.1383854</v>
       </c>
       <c r="N58">
-        <v>-145.1842032</v>
+        <v>-148.8883854</v>
       </c>
       <c r="O58">
-        <v>-36.29605080000001</v>
+        <v>-37.22209635000001</v>
       </c>
       <c r="P58">
-        <v>-108.8881524</v>
+        <v>-111.66628905</v>
       </c>
       <c r="Q58">
-        <v>-107.3881524</v>
+        <v>-110.16628905</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09558882742766375</v>
+        <v>0.09674670713528385</v>
       </c>
       <c r="T58">
-        <v>0.9704769184609243</v>
+        <v>0.9930461491228064</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07502378951939397</v>
+        <v>0.07370758268572039</v>
       </c>
       <c r="W58">
-        <v>0.2181093904313269</v>
+        <v>0.2184197520027071</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3000951580775758</v>
+        <v>0.2948303307428816</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1661003427097151</v>
+        <v>0.1680003427097151</v>
       </c>
       <c r="C59">
-        <v>-339.3444509084962</v>
+        <v>-358.6446048573548</v>
       </c>
       <c r="D59">
-        <v>230.9685490915039</v>
+        <v>227.3773951426453</v>
       </c>
       <c r="E59">
-        <v>656.7130000000001</v>
+        <v>672.4220000000001</v>
       </c>
       <c r="F59">
-        <v>895.4130000000001</v>
+        <v>911.1220000000002</v>
       </c>
       <c r="G59">
         <v>325.1</v>
@@ -6381,37 +6381,37 @@
         <v>62.25</v>
       </c>
       <c r="M59">
-        <v>211.1383854</v>
+        <v>214.8425676000001</v>
       </c>
       <c r="N59">
-        <v>-148.8883854</v>
+        <v>-152.5925676000001</v>
       </c>
       <c r="O59">
-        <v>-37.22209635000001</v>
+        <v>-38.14814190000001</v>
       </c>
       <c r="P59">
-        <v>-111.66628905</v>
+        <v>-114.4444257</v>
       </c>
       <c r="Q59">
-        <v>-110.16628905</v>
+        <v>-112.9444257</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09674670713528385</v>
+        <v>0.09795972397183822</v>
       </c>
       <c r="T59">
-        <v>0.9930461491228064</v>
+        <v>1.016690105054302</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07370758268572039</v>
+        <v>0.07243676229458727</v>
       </c>
       <c r="W59">
-        <v>0.2184197520027071</v>
+        <v>0.2187194114509363</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2948303307428816</v>
+        <v>0.289747049178349</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1680003427097151</v>
+        <v>0.1699003427097151</v>
       </c>
       <c r="C60">
-        <v>-358.6446048573546</v>
+        <v>-377.8347962975876</v>
       </c>
       <c r="D60">
-        <v>227.3773951426453</v>
+        <v>223.8962037024125</v>
       </c>
       <c r="E60">
-        <v>672.4219999999999</v>
+        <v>688.131</v>
       </c>
       <c r="F60">
-        <v>911.122</v>
+        <v>926.831</v>
       </c>
       <c r="G60">
         <v>325.1</v>
@@ -6463,37 +6463,37 @@
         <v>62.25</v>
       </c>
       <c r="M60">
-        <v>214.8425676</v>
+        <v>218.5467498</v>
       </c>
       <c r="N60">
-        <v>-152.5925676</v>
+        <v>-156.2967498</v>
       </c>
       <c r="O60">
-        <v>-38.1481419</v>
+        <v>-39.07418745</v>
       </c>
       <c r="P60">
-        <v>-114.4444257</v>
+        <v>-117.22256235</v>
       </c>
       <c r="Q60">
-        <v>-112.9444257</v>
+        <v>-115.72256235</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09795972397183822</v>
+        <v>0.09923191236139525</v>
       </c>
       <c r="T60">
-        <v>1.016690105054302</v>
+        <v>1.041487424689772</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07243676229458729</v>
+        <v>0.07120902056078071</v>
       </c>
       <c r="W60">
-        <v>0.2187194114509363</v>
+        <v>0.2190089129517679</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2897470491783491</v>
+        <v>0.2848360822431228</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1699003427097151</v>
+        <v>0.1718003427097151</v>
       </c>
       <c r="C61">
-        <v>-377.8347962975876</v>
+        <v>-396.9199997101024</v>
       </c>
       <c r="D61">
-        <v>223.8962037024125</v>
+        <v>220.5200002898976</v>
       </c>
       <c r="E61">
-        <v>688.131</v>
+        <v>703.8399999999999</v>
       </c>
       <c r="F61">
-        <v>926.831</v>
+        <v>942.54</v>
       </c>
       <c r="G61">
         <v>325.1</v>
@@ -6545,37 +6545,37 @@
         <v>62.25</v>
       </c>
       <c r="M61">
-        <v>218.5467498</v>
+        <v>222.250932</v>
       </c>
       <c r="N61">
-        <v>-156.2967498</v>
+        <v>-160.000932</v>
       </c>
       <c r="O61">
-        <v>-39.07418745</v>
+        <v>-40.000233</v>
       </c>
       <c r="P61">
-        <v>-117.22256235</v>
+        <v>-120.000699</v>
       </c>
       <c r="Q61">
-        <v>-115.72256235</v>
+        <v>-118.500699</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09923191236139525</v>
+        <v>0.1005677101704301</v>
       </c>
       <c r="T61">
-        <v>1.041487424689772</v>
+        <v>1.067524610307017</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07120902056078071</v>
+        <v>0.07002220355143438</v>
       </c>
       <c r="W61">
-        <v>0.2190089129517679</v>
+        <v>0.2192887644025718</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2848360822431228</v>
+        <v>0.2800888142057375</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1718003427097151</v>
+        <v>0.1737003427097151</v>
       </c>
       <c r="C62">
-        <v>-396.9199997101024</v>
+        <v>-415.9048939858649</v>
       </c>
       <c r="D62">
-        <v>220.5200002898976</v>
+        <v>217.2441060141351</v>
       </c>
       <c r="E62">
-        <v>703.8399999999999</v>
+        <v>719.549</v>
       </c>
       <c r="F62">
-        <v>942.54</v>
+        <v>958.249</v>
       </c>
       <c r="G62">
         <v>325.1</v>
@@ -6627,37 +6627,37 @@
         <v>62.25</v>
       </c>
       <c r="M62">
-        <v>222.250932</v>
+        <v>225.9551142</v>
       </c>
       <c r="N62">
-        <v>-160.000932</v>
+        <v>-163.7051142</v>
       </c>
       <c r="O62">
-        <v>-40.000233</v>
+        <v>-40.92627855000001</v>
       </c>
       <c r="P62">
-        <v>-120.000699</v>
+        <v>-122.77883565</v>
       </c>
       <c r="Q62">
-        <v>-118.500699</v>
+        <v>-121.27883565</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1005677101704301</v>
+        <v>0.1019720104312104</v>
       </c>
       <c r="T62">
-        <v>1.067524610307017</v>
+        <v>1.094897036212325</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07002220355143438</v>
+        <v>0.06887429857518135</v>
       </c>
       <c r="W62">
-        <v>0.2192887644025718</v>
+        <v>0.2195594403959722</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2800888142057375</v>
+        <v>0.2754971943007254</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1737003427097151</v>
+        <v>0.1756003427097151</v>
       </c>
       <c r="C63">
-        <v>-415.9048939858649</v>
+        <v>-434.7938840599278</v>
       </c>
       <c r="D63">
-        <v>217.2441060141351</v>
+        <v>214.0641159400723</v>
       </c>
       <c r="E63">
-        <v>719.549</v>
+        <v>735.258</v>
       </c>
       <c r="F63">
-        <v>958.249</v>
+        <v>973.9580000000001</v>
       </c>
       <c r="G63">
         <v>325.1</v>
@@ -6709,37 +6709,37 @@
         <v>62.25</v>
       </c>
       <c r="M63">
-        <v>225.9551142</v>
+        <v>229.6592964</v>
       </c>
       <c r="N63">
-        <v>-163.7051142</v>
+        <v>-167.4092964</v>
       </c>
       <c r="O63">
-        <v>-40.92627855000001</v>
+        <v>-41.8523241</v>
       </c>
       <c r="P63">
-        <v>-122.77883565</v>
+        <v>-125.5569723</v>
       </c>
       <c r="Q63">
-        <v>-121.27883565</v>
+        <v>-124.0569723</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1019720104312104</v>
+        <v>0.1034502212320317</v>
       </c>
       <c r="T63">
-        <v>1.094897036212325</v>
+        <v>1.123710116112649</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06887429857518135</v>
+        <v>0.06776342279171069</v>
       </c>
       <c r="W63">
-        <v>0.2195594403959722</v>
+        <v>0.2198213849057146</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2754971943007254</v>
+        <v>0.2710536911668427</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1756003427097151</v>
+        <v>0.1775003427097151</v>
       </c>
       <c r="C64">
-        <v>-434.7938840599278</v>
+        <v>-453.5911206728164</v>
       </c>
       <c r="D64">
-        <v>214.0641159400723</v>
+        <v>210.9758793271836</v>
       </c>
       <c r="E64">
-        <v>735.258</v>
+        <v>750.967</v>
       </c>
       <c r="F64">
-        <v>973.9580000000001</v>
+        <v>989.667</v>
       </c>
       <c r="G64">
         <v>325.1</v>
@@ -6791,37 +6791,37 @@
         <v>62.25</v>
       </c>
       <c r="M64">
-        <v>229.6592964</v>
+        <v>233.3634786</v>
       </c>
       <c r="N64">
-        <v>-167.4092964</v>
+        <v>-171.1134786</v>
       </c>
       <c r="O64">
-        <v>-41.8523241</v>
+        <v>-42.77836965</v>
       </c>
       <c r="P64">
-        <v>-125.5569723</v>
+        <v>-128.33510895</v>
       </c>
       <c r="Q64">
-        <v>-124.0569723</v>
+        <v>-126.83510895</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1034502212320317</v>
+        <v>0.1050083353193839</v>
       </c>
       <c r="T64">
-        <v>1.123710116112649</v>
+        <v>1.154080659791369</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06776342279171069</v>
+        <v>0.06668781290612798</v>
       </c>
       <c r="W64">
-        <v>0.2198213849057146</v>
+        <v>0.220075013716735</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2710536911668427</v>
+        <v>0.2667512516245119</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1775003427097151</v>
+        <v>0.1794003427097151</v>
       </c>
       <c r="C65">
-        <v>-453.5911206728164</v>
+        <v>-472.3005184456921</v>
       </c>
       <c r="D65">
-        <v>210.9758793271836</v>
+        <v>207.9754815543079</v>
       </c>
       <c r="E65">
-        <v>750.967</v>
+        <v>766.676</v>
       </c>
       <c r="F65">
-        <v>989.667</v>
+        <v>1005.376</v>
       </c>
       <c r="G65">
         <v>325.1</v>
@@ -6873,37 +6873,37 @@
         <v>62.25</v>
       </c>
       <c r="M65">
-        <v>233.3634786</v>
+        <v>237.0676608</v>
       </c>
       <c r="N65">
-        <v>-171.1134786</v>
+        <v>-174.8176608</v>
       </c>
       <c r="O65">
-        <v>-42.77836965</v>
+        <v>-43.70441520000001</v>
       </c>
       <c r="P65">
-        <v>-128.33510895</v>
+        <v>-131.1132456</v>
       </c>
       <c r="Q65">
-        <v>-126.83510895</v>
+        <v>-129.6132456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1050083353193839</v>
+        <v>0.1066530113004779</v>
       </c>
       <c r="T65">
-        <v>1.154080659791369</v>
+        <v>1.186138455896685</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06668781290612798</v>
+        <v>0.06564581582946973</v>
       </c>
       <c r="W65">
-        <v>0.220075013716735</v>
+        <v>0.220320716627411</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2667512516245119</v>
+        <v>0.2625832633178788</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1794003427097151</v>
+        <v>0.1813003427097151</v>
       </c>
       <c r="C66">
-        <v>-472.3005184456921</v>
+        <v>-490.9257724348038</v>
       </c>
       <c r="D66">
-        <v>207.9754815543079</v>
+        <v>205.0592275651964</v>
       </c>
       <c r="E66">
-        <v>766.676</v>
+        <v>782.3850000000001</v>
       </c>
       <c r="F66">
-        <v>1005.376</v>
+        <v>1021.085</v>
       </c>
       <c r="G66">
         <v>325.1</v>
@@ -6955,37 +6955,37 @@
         <v>62.25</v>
       </c>
       <c r="M66">
-        <v>237.0676608</v>
+        <v>240.771843</v>
       </c>
       <c r="N66">
-        <v>-174.8176608</v>
+        <v>-178.521843</v>
       </c>
       <c r="O66">
-        <v>-43.70441520000001</v>
+        <v>-44.63046075000001</v>
       </c>
       <c r="P66">
-        <v>-131.1132456</v>
+        <v>-133.89138225</v>
       </c>
       <c r="Q66">
-        <v>-129.6132456</v>
+        <v>-132.39138225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1066530113004779</v>
+        <v>0.1083916687662059</v>
       </c>
       <c r="T66">
-        <v>1.186138455896685</v>
+        <v>1.220028126065162</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06564581582946973</v>
+        <v>0.06463588020132403</v>
       </c>
       <c r="W66">
-        <v>0.220320716627411</v>
+        <v>0.2205588594485278</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2625832633178788</v>
+        <v>0.2585435208052961</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1813003427097151</v>
+        <v>0.1832003427097151</v>
       </c>
       <c r="C67">
-        <v>-490.9257724348038</v>
+        <v>-509.4703733124304</v>
       </c>
       <c r="D67">
-        <v>205.0592275651964</v>
+        <v>202.2236266875697</v>
       </c>
       <c r="E67">
-        <v>782.3850000000001</v>
+        <v>798.0940000000001</v>
       </c>
       <c r="F67">
-        <v>1021.085</v>
+        <v>1036.794</v>
       </c>
       <c r="G67">
         <v>325.1</v>
@@ -7037,37 +7037,37 @@
         <v>62.25</v>
       </c>
       <c r="M67">
-        <v>240.771843</v>
+        <v>244.4760252</v>
       </c>
       <c r="N67">
-        <v>-178.521843</v>
+        <v>-182.2260252</v>
       </c>
       <c r="O67">
-        <v>-44.63046075000001</v>
+        <v>-45.55650630000001</v>
       </c>
       <c r="P67">
-        <v>-133.89138225</v>
+        <v>-136.6695189</v>
       </c>
       <c r="Q67">
-        <v>-132.39138225</v>
+        <v>-135.1695189</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1083916687662059</v>
+        <v>0.110232600200506</v>
       </c>
       <c r="T67">
-        <v>1.220028126065162</v>
+        <v>1.255911306243549</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06463588020132403</v>
+        <v>0.06365654868312215</v>
       </c>
       <c r="W67">
-        <v>0.2205588594485278</v>
+        <v>0.2207897858205198</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2585435208052961</v>
+        <v>0.2546261947324886</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1832003427097151</v>
+        <v>0.1851003427097151</v>
       </c>
       <c r="C68">
-        <v>-509.4703733124304</v>
+        <v>-527.9376213054528</v>
       </c>
       <c r="D68">
-        <v>202.2236266875697</v>
+        <v>199.4653786945474</v>
       </c>
       <c r="E68">
-        <v>798.0940000000001</v>
+        <v>813.8030000000001</v>
       </c>
       <c r="F68">
-        <v>1036.794</v>
+        <v>1052.503</v>
       </c>
       <c r="G68">
         <v>325.1</v>
@@ -7119,37 +7119,37 @@
         <v>62.25</v>
       </c>
       <c r="M68">
-        <v>244.4760252</v>
+        <v>248.1802074000001</v>
       </c>
       <c r="N68">
-        <v>-182.2260252</v>
+        <v>-185.9302074000001</v>
       </c>
       <c r="O68">
-        <v>-45.55650630000001</v>
+        <v>-46.48255185000001</v>
       </c>
       <c r="P68">
-        <v>-136.6695189</v>
+        <v>-139.44765555</v>
       </c>
       <c r="Q68">
-        <v>-135.1695189</v>
+        <v>-137.94765555</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.110232600200506</v>
+        <v>0.112185103236885</v>
       </c>
       <c r="T68">
-        <v>1.255911306243549</v>
+        <v>1.293969224614566</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06365654868312215</v>
+        <v>0.062706450941583</v>
       </c>
       <c r="W68">
-        <v>0.2207897858205198</v>
+        <v>0.2210138188679747</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2546261947324886</v>
+        <v>0.250825803766332</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1851003427097151</v>
+        <v>0.1870003427097151</v>
       </c>
       <c r="C69">
-        <v>-527.9376213054528</v>
+        <v>-546.3306390085739</v>
       </c>
       <c r="D69">
-        <v>199.4653786945474</v>
+        <v>196.7813609914263</v>
       </c>
       <c r="E69">
-        <v>813.8030000000001</v>
+        <v>829.5120000000002</v>
       </c>
       <c r="F69">
-        <v>1052.503</v>
+        <v>1068.212</v>
       </c>
       <c r="G69">
         <v>325.1</v>
@@ -7201,37 +7201,37 @@
         <v>62.25</v>
       </c>
       <c r="M69">
-        <v>248.1802074000001</v>
+        <v>251.8843896</v>
       </c>
       <c r="N69">
-        <v>-185.9302074000001</v>
+        <v>-189.6343896</v>
       </c>
       <c r="O69">
-        <v>-46.48255185000001</v>
+        <v>-47.40859740000001</v>
       </c>
       <c r="P69">
-        <v>-139.44765555</v>
+        <v>-142.2257922</v>
       </c>
       <c r="Q69">
-        <v>-137.94765555</v>
+        <v>-140.7257922</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.112185103236885</v>
+        <v>0.1142596377130377</v>
       </c>
       <c r="T69">
-        <v>1.293969224614566</v>
+        <v>1.334405762883771</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.062706450941583</v>
+        <v>0.06178429725126561</v>
       </c>
       <c r="W69">
-        <v>0.2210138188679747</v>
+        <v>0.2212312627081516</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.250825803766332</v>
+        <v>0.2471371890050624</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1870003427097151</v>
+        <v>0.1889003427097151</v>
       </c>
       <c r="C70">
-        <v>-546.3306390085739</v>
+        <v>-564.652383176784</v>
       </c>
       <c r="D70">
-        <v>196.7813609914263</v>
+        <v>194.168616823216</v>
       </c>
       <c r="E70">
-        <v>829.5120000000002</v>
+        <v>845.221</v>
       </c>
       <c r="F70">
-        <v>1068.212</v>
+        <v>1083.921</v>
       </c>
       <c r="G70">
         <v>325.1</v>
@@ -7283,37 +7283,37 @@
         <v>62.25</v>
       </c>
       <c r="M70">
-        <v>251.8843896</v>
+        <v>255.5885718</v>
       </c>
       <c r="N70">
-        <v>-189.6343896</v>
+        <v>-193.3385718</v>
       </c>
       <c r="O70">
-        <v>-47.40859740000001</v>
+        <v>-48.33464295</v>
       </c>
       <c r="P70">
-        <v>-142.2257922</v>
+        <v>-145.00392885</v>
       </c>
       <c r="Q70">
-        <v>-140.7257922</v>
+        <v>-143.50392885</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1142596377130377</v>
+        <v>0.1164680131231357</v>
       </c>
       <c r="T70">
-        <v>1.334405762883771</v>
+        <v>1.37745111007357</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06178429725126561</v>
+        <v>0.0608888726534212</v>
       </c>
       <c r="W70">
-        <v>0.2212312627081516</v>
+        <v>0.2214424038283233</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2471371890050624</v>
+        <v>0.2435554906136848</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1889003427097151</v>
+        <v>0.1908003427097151</v>
       </c>
       <c r="C71">
-        <v>-564.652383176784</v>
+        <v>-582.9056555906961</v>
       </c>
       <c r="D71">
-        <v>194.168616823216</v>
+        <v>191.624344409304</v>
       </c>
       <c r="E71">
-        <v>845.221</v>
+        <v>860.9300000000001</v>
       </c>
       <c r="F71">
-        <v>1083.921</v>
+        <v>1099.63</v>
       </c>
       <c r="G71">
         <v>325.1</v>
@@ -7365,37 +7365,37 @@
         <v>62.25</v>
       </c>
       <c r="M71">
-        <v>255.5885718</v>
+        <v>259.2927540000001</v>
       </c>
       <c r="N71">
-        <v>-193.3385718</v>
+        <v>-197.0427540000001</v>
       </c>
       <c r="O71">
-        <v>-48.33464295</v>
+        <v>-49.26068850000001</v>
       </c>
       <c r="P71">
-        <v>-145.00392885</v>
+        <v>-147.7820655</v>
       </c>
       <c r="Q71">
-        <v>-143.50392885</v>
+        <v>-146.2820655</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1164680131231357</v>
+        <v>0.1188236135605735</v>
       </c>
       <c r="T71">
-        <v>1.37745111007357</v>
+        <v>1.423366147076023</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0608888726534212</v>
+        <v>0.06001903161551517</v>
       </c>
       <c r="W71">
-        <v>0.2214424038283233</v>
+        <v>0.2216475123450615</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2435554906136848</v>
+        <v>0.2400761264620607</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1908003427097151</v>
+        <v>0.1927003427097151</v>
       </c>
       <c r="C72">
-        <v>-582.9056555906961</v>
+        <v>-601.0931130786894</v>
       </c>
       <c r="D72">
-        <v>191.624344409304</v>
+        <v>189.1458869213108</v>
       </c>
       <c r="E72">
-        <v>860.9300000000001</v>
+        <v>876.6390000000001</v>
       </c>
       <c r="F72">
-        <v>1099.63</v>
+        <v>1115.339</v>
       </c>
       <c r="G72">
         <v>325.1</v>
@@ -7447,37 +7447,37 @@
         <v>62.25</v>
       </c>
       <c r="M72">
-        <v>259.2927540000001</v>
+        <v>262.9969362000001</v>
       </c>
       <c r="N72">
-        <v>-197.0427540000001</v>
+        <v>-200.7469362000001</v>
       </c>
       <c r="O72">
-        <v>-49.26068850000001</v>
+        <v>-50.18673405000001</v>
       </c>
       <c r="P72">
-        <v>-147.7820655</v>
+        <v>-150.56020215</v>
       </c>
       <c r="Q72">
-        <v>-146.2820655</v>
+        <v>-149.06020215</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1188236135605735</v>
+        <v>0.1213416692005933</v>
       </c>
       <c r="T72">
-        <v>1.423366147076023</v>
+        <v>1.472447738354506</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06001903161551517</v>
+        <v>0.05917369314205721</v>
       </c>
       <c r="W72">
-        <v>0.2216475123450615</v>
+        <v>0.2218468431571029</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2400761264620607</v>
+        <v>0.2366947725682288</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1927003427097151</v>
+        <v>0.1946003427097151</v>
       </c>
       <c r="C73">
-        <v>-601.0931130786892</v>
+        <v>-619.2172767712325</v>
       </c>
       <c r="D73">
-        <v>189.1458869213108</v>
+        <v>186.7307232287675</v>
       </c>
       <c r="E73">
-        <v>876.6389999999999</v>
+        <v>892.348</v>
       </c>
       <c r="F73">
-        <v>1115.339</v>
+        <v>1131.048</v>
       </c>
       <c r="G73">
         <v>325.1</v>
@@ -7529,37 +7529,37 @@
         <v>62.25</v>
       </c>
       <c r="M73">
-        <v>262.9969362</v>
+        <v>266.7011184</v>
       </c>
       <c r="N73">
-        <v>-200.7469362</v>
+        <v>-204.4511184</v>
       </c>
       <c r="O73">
-        <v>-50.18673405</v>
+        <v>-51.1127796</v>
       </c>
       <c r="P73">
-        <v>-150.56020215</v>
+        <v>-153.3383388</v>
       </c>
       <c r="Q73">
-        <v>-149.06020215</v>
+        <v>-151.8383388</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1213416692005933</v>
+        <v>0.1240395859577573</v>
       </c>
       <c r="T73">
-        <v>1.472447738354506</v>
+        <v>1.525035157581452</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05917369314205722</v>
+        <v>0.05835183629286198</v>
       </c>
       <c r="W73">
-        <v>0.2218468431571029</v>
+        <v>0.2220406370021432</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2366947725682289</v>
+        <v>0.2334073451714479</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1946003427097151</v>
+        <v>0.1965003427097151</v>
       </c>
       <c r="C74">
-        <v>-619.2172767712325</v>
+        <v>-637.2805406551447</v>
       </c>
       <c r="D74">
-        <v>186.7307232287675</v>
+        <v>184.3764593448554</v>
       </c>
       <c r="E74">
-        <v>892.348</v>
+        <v>908.057</v>
       </c>
       <c r="F74">
-        <v>1131.048</v>
+        <v>1146.757</v>
       </c>
       <c r="G74">
         <v>325.1</v>
@@ -7611,37 +7611,37 @@
         <v>62.25</v>
       </c>
       <c r="M74">
-        <v>266.7011184</v>
+        <v>270.4053006</v>
       </c>
       <c r="N74">
-        <v>-204.4511184</v>
+        <v>-208.1553006</v>
       </c>
       <c r="O74">
-        <v>-51.1127796</v>
+        <v>-52.03882515000001</v>
       </c>
       <c r="P74">
-        <v>-153.3383388</v>
+        <v>-156.11647545</v>
       </c>
       <c r="Q74">
-        <v>-151.8383388</v>
+        <v>-154.61647545</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1240395859577573</v>
+        <v>0.1269373484006372</v>
       </c>
       <c r="T74">
-        <v>1.525035157581452</v>
+        <v>1.58151794119558</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05835183629286198</v>
+        <v>0.05755249606967208</v>
       </c>
       <c r="W74">
-        <v>0.2220406370021432</v>
+        <v>0.2222291214267713</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2334073451714479</v>
+        <v>0.2302099842786883</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1965003427097151</v>
+        <v>0.1984003427097151</v>
       </c>
       <c r="C75">
-        <v>-637.2805406551447</v>
+        <v>-655.2851794888111</v>
       </c>
       <c r="D75">
-        <v>184.3764593448554</v>
+        <v>182.0808205111891</v>
       </c>
       <c r="E75">
-        <v>908.057</v>
+        <v>923.7660000000001</v>
       </c>
       <c r="F75">
-        <v>1146.757</v>
+        <v>1162.466</v>
       </c>
       <c r="G75">
         <v>325.1</v>
@@ -7693,37 +7693,37 @@
         <v>62.25</v>
       </c>
       <c r="M75">
-        <v>270.4053006</v>
+        <v>274.1094828</v>
       </c>
       <c r="N75">
-        <v>-208.1553006</v>
+        <v>-211.8594828</v>
       </c>
       <c r="O75">
-        <v>-52.03882515000001</v>
+        <v>-52.96487070000001</v>
       </c>
       <c r="P75">
-        <v>-156.11647545</v>
+        <v>-158.8946121</v>
       </c>
       <c r="Q75">
-        <v>-154.61647545</v>
+        <v>-157.3946121</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1269373484006372</v>
+        <v>0.1300580156468156</v>
       </c>
       <c r="T75">
-        <v>1.58151794119558</v>
+        <v>1.642345554318487</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05755249606967208</v>
+        <v>0.05677475963629814</v>
       </c>
       <c r="W75">
-        <v>0.2222291214267713</v>
+        <v>0.2224125116777609</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2302099842786883</v>
+        <v>0.2270990385451925</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1984003427097151</v>
+        <v>0.2003003427097151</v>
       </c>
       <c r="C76">
-        <v>-655.2851794888111</v>
+        <v>-673.2333561333655</v>
       </c>
       <c r="D76">
-        <v>182.0808205111891</v>
+        <v>179.8416438666346</v>
       </c>
       <c r="E76">
-        <v>923.7660000000001</v>
+        <v>939.4750000000001</v>
       </c>
       <c r="F76">
-        <v>1162.466</v>
+        <v>1178.175</v>
       </c>
       <c r="G76">
         <v>325.1</v>
@@ -7775,37 +7775,37 @@
         <v>62.25</v>
       </c>
       <c r="M76">
-        <v>274.1094828</v>
+        <v>277.8136650000001</v>
       </c>
       <c r="N76">
-        <v>-211.8594828</v>
+        <v>-215.5636650000001</v>
       </c>
       <c r="O76">
-        <v>-52.96487070000001</v>
+        <v>-53.89091625000002</v>
       </c>
       <c r="P76">
-        <v>-158.8946121</v>
+        <v>-161.67274875</v>
       </c>
       <c r="Q76">
-        <v>-157.3946121</v>
+        <v>-160.17274875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1300580156468156</v>
+        <v>0.1334283362726882</v>
       </c>
       <c r="T76">
-        <v>1.642345554318487</v>
+        <v>1.708039376491227</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05677475963629814</v>
+        <v>0.05601776284114748</v>
       </c>
       <c r="W76">
-        <v>0.2224125116777609</v>
+        <v>0.2225910115220574</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2270990385451925</v>
+        <v>0.2240710513645899</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2003003427097151</v>
+        <v>0.2022003427097151</v>
       </c>
       <c r="C77">
-        <v>-673.2333561333655</v>
+        <v>-691.1271283495032</v>
       </c>
       <c r="D77">
-        <v>179.8416438666346</v>
+        <v>177.6568716504967</v>
       </c>
       <c r="E77">
-        <v>939.4750000000001</v>
+        <v>955.184</v>
       </c>
       <c r="F77">
-        <v>1178.175</v>
+        <v>1193.884</v>
       </c>
       <c r="G77">
         <v>325.1</v>
@@ -7857,37 +7857,37 @@
         <v>62.25</v>
       </c>
       <c r="M77">
-        <v>277.8136650000001</v>
+        <v>281.5178472</v>
       </c>
       <c r="N77">
-        <v>-215.5636650000001</v>
+        <v>-219.2678472</v>
       </c>
       <c r="O77">
-        <v>-53.89091625000002</v>
+        <v>-54.8169618</v>
       </c>
       <c r="P77">
-        <v>-161.67274875</v>
+        <v>-164.4508854</v>
       </c>
       <c r="Q77">
-        <v>-160.17274875</v>
+        <v>-162.9508854</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1334283362726882</v>
+        <v>0.1370795169507169</v>
       </c>
       <c r="T77">
-        <v>1.708039376491227</v>
+        <v>1.779207683845028</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05601776284114748</v>
+        <v>0.05528068701429029</v>
       </c>
       <c r="W77">
-        <v>0.2225910115220574</v>
+        <v>0.2227648140020304</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2240710513645899</v>
+        <v>0.2211227480571611</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2022003427097151</v>
+        <v>0.2041003427097152</v>
       </c>
       <c r="C78">
-        <v>-691.1271283495032</v>
+        <v>-708.9684551048214</v>
       </c>
       <c r="D78">
-        <v>177.6568716504967</v>
+        <v>175.5245448951786</v>
       </c>
       <c r="E78">
-        <v>955.184</v>
+        <v>970.893</v>
       </c>
       <c r="F78">
-        <v>1193.884</v>
+        <v>1209.593</v>
       </c>
       <c r="G78">
         <v>325.1</v>
@@ -7939,37 +7939,37 @@
         <v>62.25</v>
       </c>
       <c r="M78">
-        <v>281.5178472</v>
+        <v>285.2220294000001</v>
       </c>
       <c r="N78">
-        <v>-219.2678472</v>
+        <v>-222.9720294000001</v>
       </c>
       <c r="O78">
-        <v>-54.8169618</v>
+        <v>-55.74300735000001</v>
       </c>
       <c r="P78">
-        <v>-164.4508854</v>
+        <v>-167.22902205</v>
       </c>
       <c r="Q78">
-        <v>-162.9508854</v>
+        <v>-165.72902205</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1370795169507169</v>
+        <v>0.1410481916007481</v>
       </c>
       <c r="T78">
-        <v>1.779207683845028</v>
+        <v>1.856564539664377</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05528068701429029</v>
+        <v>0.0545627560141047</v>
       </c>
       <c r="W78">
-        <v>0.2227648140020304</v>
+        <v>0.2229341021318741</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2211227480571611</v>
+        <v>0.2182510240564188</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2041003427097152</v>
+        <v>0.2060003427097152</v>
       </c>
       <c r="C79">
-        <v>-708.9684551048214</v>
+        <v>-726.7592024323234</v>
       </c>
       <c r="D79">
-        <v>175.5245448951786</v>
+        <v>173.4427975676768</v>
       </c>
       <c r="E79">
-        <v>970.893</v>
+        <v>986.6020000000001</v>
       </c>
       <c r="F79">
-        <v>1209.593</v>
+        <v>1225.302</v>
       </c>
       <c r="G79">
         <v>325.1</v>
@@ -8021,37 +8021,37 @@
         <v>62.25</v>
       </c>
       <c r="M79">
-        <v>285.2220294000001</v>
+        <v>288.9262116</v>
       </c>
       <c r="N79">
-        <v>-222.9720294000001</v>
+        <v>-226.6762116</v>
       </c>
       <c r="O79">
-        <v>-55.74300735000001</v>
+        <v>-56.66905290000001</v>
       </c>
       <c r="P79">
-        <v>-167.22902205</v>
+        <v>-170.0071587</v>
       </c>
       <c r="Q79">
-        <v>-165.72902205</v>
+        <v>-168.5071587</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1410481916007481</v>
+        <v>0.1453776548553275</v>
       </c>
       <c r="T79">
-        <v>1.856564539664377</v>
+        <v>1.940953836921849</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0545627560141047</v>
+        <v>0.05386323350110336</v>
       </c>
       <c r="W79">
-        <v>0.2229341021318741</v>
+        <v>0.2230990495404399</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2182510240564188</v>
+        <v>0.2154529340044135</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2060003427097152</v>
+        <v>0.2079003427097151</v>
       </c>
       <c r="C80">
-        <v>-726.7592024323234</v>
+        <v>-744.5011488769137</v>
       </c>
       <c r="D80">
-        <v>173.4427975676768</v>
+        <v>171.4098511230865</v>
       </c>
       <c r="E80">
-        <v>986.6020000000001</v>
+        <v>1002.311</v>
       </c>
       <c r="F80">
-        <v>1225.302</v>
+        <v>1241.011</v>
       </c>
       <c r="G80">
         <v>325.1</v>
@@ -8103,37 +8103,37 @@
         <v>62.25</v>
       </c>
       <c r="M80">
-        <v>288.9262116</v>
+        <v>292.6303938</v>
       </c>
       <c r="N80">
-        <v>-226.6762116</v>
+        <v>-230.3803938</v>
       </c>
       <c r="O80">
-        <v>-56.66905290000001</v>
+        <v>-57.59509845000001</v>
       </c>
       <c r="P80">
-        <v>-170.0071587</v>
+        <v>-172.78529535</v>
       </c>
       <c r="Q80">
-        <v>-168.5071587</v>
+        <v>-171.28529535</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1453776548553275</v>
+        <v>0.1501194479436765</v>
       </c>
       <c r="T80">
-        <v>1.940953836921849</v>
+        <v>2.033380210108604</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05386323350110336</v>
+        <v>0.05318142041881091</v>
       </c>
       <c r="W80">
-        <v>0.2230990495404399</v>
+        <v>0.2232598210652444</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2154529340044135</v>
+        <v>0.2127256816752436</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2079003427097151</v>
+        <v>0.2098003427097151</v>
       </c>
       <c r="C81">
-        <v>-744.5011488769137</v>
+        <v>-762.1959905632957</v>
       </c>
       <c r="D81">
-        <v>171.4098511230865</v>
+        <v>169.4240094367046</v>
       </c>
       <c r="E81">
-        <v>1002.311</v>
+        <v>1018.02</v>
       </c>
       <c r="F81">
-        <v>1241.011</v>
+        <v>1256.72</v>
       </c>
       <c r="G81">
         <v>325.1</v>
@@ -8185,37 +8185,37 @@
         <v>62.25</v>
       </c>
       <c r="M81">
-        <v>292.6303938</v>
+        <v>296.3345760000001</v>
       </c>
       <c r="N81">
-        <v>-230.3803938</v>
+        <v>-234.0845760000001</v>
       </c>
       <c r="O81">
-        <v>-57.59509845000001</v>
+        <v>-58.52114400000002</v>
       </c>
       <c r="P81">
-        <v>-172.78529535</v>
+        <v>-175.5634320000001</v>
       </c>
       <c r="Q81">
-        <v>-171.28529535</v>
+        <v>-174.0634320000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1501194479436765</v>
+        <v>0.1553354203408603</v>
       </c>
       <c r="T81">
-        <v>2.033380210108604</v>
+        <v>2.135049220614034</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05318142041881091</v>
+        <v>0.05251665266357577</v>
       </c>
       <c r="W81">
-        <v>0.2232598210652444</v>
+        <v>0.2234165733019289</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2127256816752436</v>
+        <v>0.2100666106543031</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2098003427097151</v>
+        <v>0.2117003427097152</v>
       </c>
       <c r="C82">
-        <v>-762.1959905632957</v>
+        <v>-779.8453459156228</v>
       </c>
       <c r="D82">
-        <v>169.4240094367046</v>
+        <v>167.4836540843773</v>
       </c>
       <c r="E82">
-        <v>1018.02</v>
+        <v>1033.729</v>
       </c>
       <c r="F82">
-        <v>1256.72</v>
+        <v>1272.429</v>
       </c>
       <c r="G82">
         <v>325.1</v>
@@ -8267,37 +8267,37 @@
         <v>62.25</v>
       </c>
       <c r="M82">
-        <v>296.3345760000001</v>
+        <v>300.0387582</v>
       </c>
       <c r="N82">
-        <v>-234.0845760000001</v>
+        <v>-237.7887582</v>
       </c>
       <c r="O82">
-        <v>-58.52114400000002</v>
+        <v>-59.44718955</v>
       </c>
       <c r="P82">
-        <v>-175.5634320000001</v>
+        <v>-178.34156865</v>
       </c>
       <c r="Q82">
-        <v>-174.0634320000001</v>
+        <v>-176.84156865</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1553354203408603</v>
+        <v>0.1611004424640635</v>
       </c>
       <c r="T82">
-        <v>2.135049220614034</v>
+        <v>2.247420232225299</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05251665266357577</v>
+        <v>0.05186829892698842</v>
       </c>
       <c r="W82">
-        <v>0.2234165733019289</v>
+        <v>0.2235694551130162</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2100666106543031</v>
+        <v>0.2074731957079536</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2117003427097152</v>
+        <v>0.2136003427097151</v>
       </c>
       <c r="C83">
-        <v>-779.8453459156228</v>
+        <v>-797.4507600565094</v>
       </c>
       <c r="D83">
-        <v>167.4836540843773</v>
+        <v>165.5872399434907</v>
       </c>
       <c r="E83">
-        <v>1033.729</v>
+        <v>1049.438</v>
       </c>
       <c r="F83">
-        <v>1272.429</v>
+        <v>1288.138</v>
       </c>
       <c r="G83">
         <v>325.1</v>
@@ -8349,37 +8349,37 @@
         <v>62.25</v>
       </c>
       <c r="M83">
-        <v>300.0387582</v>
+        <v>303.7429404000001</v>
       </c>
       <c r="N83">
-        <v>-237.7887582</v>
+        <v>-241.4929404000001</v>
       </c>
       <c r="O83">
-        <v>-59.44718955</v>
+        <v>-60.37323510000002</v>
       </c>
       <c r="P83">
-        <v>-178.34156865</v>
+        <v>-181.1197053</v>
       </c>
       <c r="Q83">
-        <v>-176.84156865</v>
+        <v>-179.6197053</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1611004424640635</v>
+        <v>0.1675060226009559</v>
       </c>
       <c r="T83">
-        <v>2.247420232225299</v>
+        <v>2.372276911793371</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05186829892698842</v>
+        <v>0.05123575869617148</v>
       </c>
       <c r="W83">
-        <v>0.2235694551130162</v>
+        <v>0.2237186080994428</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2074731957079536</v>
+        <v>0.2049430347846859</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2136003427097151</v>
+        <v>0.2155003427097151</v>
       </c>
       <c r="C84">
-        <v>-797.4507600565094</v>
+        <v>-815.0137089105244</v>
       </c>
       <c r="D84">
-        <v>165.5872399434907</v>
+        <v>163.7332910894757</v>
       </c>
       <c r="E84">
-        <v>1049.438</v>
+        <v>1065.147</v>
       </c>
       <c r="F84">
-        <v>1288.138</v>
+        <v>1303.847</v>
       </c>
       <c r="G84">
         <v>325.1</v>
@@ -8431,37 +8431,37 @@
         <v>62.25</v>
       </c>
       <c r="M84">
-        <v>303.7429404000001</v>
+        <v>307.4471226000001</v>
       </c>
       <c r="N84">
-        <v>-241.4929404000001</v>
+        <v>-245.1971226000001</v>
       </c>
       <c r="O84">
-        <v>-60.37323510000002</v>
+        <v>-61.29928065000001</v>
       </c>
       <c r="P84">
-        <v>-181.1197053</v>
+        <v>-183.89784195</v>
       </c>
       <c r="Q84">
-        <v>-179.6197053</v>
+        <v>-182.39784195</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1675060226009559</v>
+        <v>0.1746652004010121</v>
       </c>
       <c r="T84">
-        <v>2.372276911793371</v>
+        <v>2.511822612487099</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05123575869617148</v>
+        <v>0.05061846039862725</v>
       </c>
       <c r="W84">
-        <v>0.2237186080994428</v>
+        <v>0.2238641670380037</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2049430347846859</v>
+        <v>0.202473841594509</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2155003427097151</v>
+        <v>0.2174003427097151</v>
       </c>
       <c r="C85">
-        <v>-815.0137089105244</v>
+        <v>-832.5356030350792</v>
       </c>
       <c r="D85">
-        <v>163.7332910894757</v>
+        <v>161.920396964921</v>
       </c>
       <c r="E85">
-        <v>1065.147</v>
+        <v>1080.856</v>
       </c>
       <c r="F85">
-        <v>1303.847</v>
+        <v>1319.556</v>
       </c>
       <c r="G85">
         <v>325.1</v>
@@ -8513,37 +8513,37 @@
         <v>62.25</v>
       </c>
       <c r="M85">
-        <v>307.4471226000001</v>
+        <v>311.1513048</v>
       </c>
       <c r="N85">
-        <v>-245.1971226000001</v>
+        <v>-248.9013048</v>
       </c>
       <c r="O85">
-        <v>-61.29928065000001</v>
+        <v>-62.22532620000001</v>
       </c>
       <c r="P85">
-        <v>-183.89784195</v>
+        <v>-186.6759786</v>
       </c>
       <c r="Q85">
-        <v>-182.39784195</v>
+        <v>-185.1759786</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1746652004010121</v>
+        <v>0.1827192754260754</v>
       </c>
       <c r="T85">
-        <v>2.511822612487099</v>
+        <v>2.668811525767544</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05061846039862725</v>
+        <v>0.05001585967959597</v>
       </c>
       <c r="W85">
-        <v>0.2238641670380037</v>
+        <v>0.2240062602875513</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.202473841594509</v>
+        <v>0.2000634387183839</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2174003427097151</v>
+        <v>0.2193003427097151</v>
       </c>
       <c r="C86">
-        <v>-832.535603035079</v>
+        <v>-850.0177911996008</v>
       </c>
       <c r="D86">
-        <v>161.920396964921</v>
+        <v>160.1472088003993</v>
       </c>
       <c r="E86">
-        <v>1080.856</v>
+        <v>1096.565</v>
       </c>
       <c r="F86">
-        <v>1319.556</v>
+        <v>1335.265</v>
       </c>
       <c r="G86">
         <v>325.1</v>
@@ -8595,37 +8595,37 @@
         <v>62.25</v>
       </c>
       <c r="M86">
-        <v>311.1513048</v>
+        <v>314.855487</v>
       </c>
       <c r="N86">
-        <v>-248.9013048</v>
+        <v>-252.605487</v>
       </c>
       <c r="O86">
-        <v>-62.22532620000001</v>
+        <v>-63.15137175000001</v>
       </c>
       <c r="P86">
-        <v>-186.6759786</v>
+        <v>-189.45411525</v>
       </c>
       <c r="Q86">
-        <v>-185.1759786</v>
+        <v>-187.95411525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1827192754260753</v>
+        <v>0.191847227121147</v>
       </c>
       <c r="T86">
-        <v>2.668811525767541</v>
+        <v>2.846732294152045</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05001585967959597</v>
+        <v>0.0494274378010125</v>
       </c>
       <c r="W86">
-        <v>0.2240062602875513</v>
+        <v>0.2241450101665213</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2000634387183839</v>
+        <v>0.19770975120405</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2193003427097151</v>
+        <v>0.2212003427097151</v>
       </c>
       <c r="C87">
-        <v>-850.0177911996008</v>
+        <v>-867.4615637320831</v>
       </c>
       <c r="D87">
-        <v>160.1472088003993</v>
+        <v>158.4124362679171</v>
       </c>
       <c r="E87">
-        <v>1096.565</v>
+        <v>1112.274</v>
       </c>
       <c r="F87">
-        <v>1335.265</v>
+        <v>1350.974</v>
       </c>
       <c r="G87">
         <v>325.1</v>
@@ -8677,37 +8677,37 @@
         <v>62.25</v>
       </c>
       <c r="M87">
-        <v>314.855487</v>
+        <v>318.5596692</v>
       </c>
       <c r="N87">
-        <v>-252.605487</v>
+        <v>-256.3096692</v>
       </c>
       <c r="O87">
-        <v>-63.15137175000001</v>
+        <v>-64.07741730000001</v>
       </c>
       <c r="P87">
-        <v>-189.45411525</v>
+        <v>-192.2322519</v>
       </c>
       <c r="Q87">
-        <v>-187.95411525</v>
+        <v>-190.7322519</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.191847227121147</v>
+        <v>0.2022791719155147</v>
       </c>
       <c r="T87">
-        <v>2.846732294152045</v>
+        <v>3.050070315162905</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0494274378010125</v>
+        <v>0.04885270015216352</v>
       </c>
       <c r="W87">
-        <v>0.2241450101665213</v>
+        <v>0.2242805333041199</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.19770975120405</v>
+        <v>0.195410800608654</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2212003427097151</v>
+        <v>0.2231003427097151</v>
       </c>
       <c r="C88">
-        <v>-867.4615637320831</v>
+        <v>-884.8681556504573</v>
       </c>
       <c r="D88">
-        <v>158.4124362679171</v>
+        <v>156.7148443495426</v>
       </c>
       <c r="E88">
-        <v>1112.274</v>
+        <v>1127.983</v>
       </c>
       <c r="F88">
-        <v>1350.974</v>
+        <v>1366.683</v>
       </c>
       <c r="G88">
         <v>325.1</v>
@@ -8759,37 +8759,37 @@
         <v>62.25</v>
       </c>
       <c r="M88">
-        <v>318.5596692</v>
+        <v>322.2638514</v>
       </c>
       <c r="N88">
-        <v>-256.3096692</v>
+        <v>-260.0138514</v>
       </c>
       <c r="O88">
-        <v>-64.07741730000001</v>
+        <v>-65.00346285000001</v>
       </c>
       <c r="P88">
-        <v>-192.2322519</v>
+        <v>-195.01038855</v>
       </c>
       <c r="Q88">
-        <v>-190.7322519</v>
+        <v>-193.51038855</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2022791719155147</v>
+        <v>0.2143160312936312</v>
       </c>
       <c r="T88">
-        <v>3.050070315162905</v>
+        <v>3.284691108636974</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04885270015216352</v>
+        <v>0.04829117486305819</v>
       </c>
       <c r="W88">
-        <v>0.2242805333041199</v>
+        <v>0.2244129409672909</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.195410800608654</v>
+        <v>0.1931646994522328</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2231003427097151</v>
+        <v>0.2250003427097151</v>
       </c>
       <c r="C89">
-        <v>-884.8681556504573</v>
+        <v>-902.238749594764</v>
       </c>
       <c r="D89">
-        <v>156.7148443495426</v>
+        <v>155.053250405236</v>
       </c>
       <c r="E89">
-        <v>1127.983</v>
+        <v>1143.692</v>
       </c>
       <c r="F89">
-        <v>1366.683</v>
+        <v>1382.392</v>
       </c>
       <c r="G89">
         <v>325.1</v>
@@ -8841,37 +8841,37 @@
         <v>62.25</v>
       </c>
       <c r="M89">
-        <v>322.2638514</v>
+        <v>325.9680336</v>
       </c>
       <c r="N89">
-        <v>-260.0138514</v>
+        <v>-263.7180336</v>
       </c>
       <c r="O89">
-        <v>-65.00346285000001</v>
+        <v>-65.9295084</v>
       </c>
       <c r="P89">
-        <v>-195.01038855</v>
+        <v>-197.7885252</v>
       </c>
       <c r="Q89">
-        <v>-193.51038855</v>
+        <v>-196.2885252</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2143160312936312</v>
+        <v>0.2283590339014338</v>
       </c>
       <c r="T89">
-        <v>3.284691108636974</v>
+        <v>3.558415367690056</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04829117486305819</v>
+        <v>0.04774241151234162</v>
       </c>
       <c r="W89">
-        <v>0.2244129409672909</v>
+        <v>0.2245423393653899</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1931646994522328</v>
+        <v>0.1909696460493665</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2250003427097151</v>
+        <v>0.2269003427097151</v>
       </c>
       <c r="C90">
-        <v>-902.238749594764</v>
+        <v>-919.5744785747426</v>
       </c>
       <c r="D90">
-        <v>155.053250405236</v>
+        <v>153.4265214252575</v>
       </c>
       <c r="E90">
-        <v>1143.692</v>
+        <v>1159.401</v>
       </c>
       <c r="F90">
-        <v>1382.392</v>
+        <v>1398.101</v>
       </c>
       <c r="G90">
         <v>325.1</v>
@@ -8923,37 +8923,37 @@
         <v>62.25</v>
       </c>
       <c r="M90">
-        <v>325.9680336</v>
+        <v>329.6722158000001</v>
       </c>
       <c r="N90">
-        <v>-263.7180336</v>
+        <v>-267.4222158000001</v>
       </c>
       <c r="O90">
-        <v>-65.9295084</v>
+        <v>-66.85555395000002</v>
       </c>
       <c r="P90">
-        <v>-197.7885252</v>
+        <v>-200.5666618500001</v>
       </c>
       <c r="Q90">
-        <v>-196.2885252</v>
+        <v>-199.0666618500001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2283590339014338</v>
+        <v>0.244955309710655</v>
       </c>
       <c r="T90">
-        <v>3.558415367690056</v>
+        <v>3.881907673843697</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04774241151234162</v>
+        <v>0.0472059799223153</v>
       </c>
       <c r="W90">
-        <v>0.2245423393653899</v>
+        <v>0.2246688299343181</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1909696460493665</v>
+        <v>0.1888239196892612</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2269003427097151</v>
+        <v>0.2288003427097151</v>
       </c>
       <c r="C91">
-        <v>-919.5744785747426</v>
+        <v>-936.8764285462648</v>
       </c>
       <c r="D91">
-        <v>153.4265214252575</v>
+        <v>151.8335714537353</v>
       </c>
       <c r="E91">
-        <v>1159.401</v>
+        <v>1175.11</v>
       </c>
       <c r="F91">
-        <v>1398.101</v>
+        <v>1413.81</v>
       </c>
       <c r="G91">
         <v>325.1</v>
@@ -9005,37 +9005,37 @@
         <v>62.25</v>
       </c>
       <c r="M91">
-        <v>329.6722158000001</v>
+        <v>333.3763980000001</v>
       </c>
       <c r="N91">
-        <v>-267.4222158000001</v>
+        <v>-271.1263980000001</v>
       </c>
       <c r="O91">
-        <v>-66.85555395000002</v>
+        <v>-67.78159950000001</v>
       </c>
       <c r="P91">
-        <v>-200.5666618500001</v>
+        <v>-203.3447985</v>
       </c>
       <c r="Q91">
-        <v>-199.0666618500001</v>
+        <v>-201.8447985</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.244955309710655</v>
+        <v>0.2648708406817206</v>
       </c>
       <c r="T91">
-        <v>3.881907673843697</v>
+        <v>4.270098441228067</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0472059799223153</v>
+        <v>0.04668146903428957</v>
       </c>
       <c r="W91">
-        <v>0.2246688299343181</v>
+        <v>0.2247925096017145</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1888239196892612</v>
+        <v>0.1867258761371583</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2288003427097151</v>
+        <v>0.2307003427097152</v>
       </c>
       <c r="C92">
-        <v>-936.8764285462648</v>
+        <v>-954.1456408289162</v>
       </c>
       <c r="D92">
-        <v>151.8335714537353</v>
+        <v>150.2733591710841</v>
       </c>
       <c r="E92">
-        <v>1175.11</v>
+        <v>1190.819</v>
       </c>
       <c r="F92">
-        <v>1413.81</v>
+        <v>1429.519</v>
       </c>
       <c r="G92">
         <v>325.1</v>
@@ -9087,37 +9087,37 @@
         <v>62.25</v>
       </c>
       <c r="M92">
-        <v>333.3763980000001</v>
+        <v>337.0805802</v>
       </c>
       <c r="N92">
-        <v>-271.1263980000001</v>
+        <v>-274.8305802</v>
       </c>
       <c r="O92">
-        <v>-67.78159950000001</v>
+        <v>-68.70764505000001</v>
       </c>
       <c r="P92">
-        <v>-203.3447985</v>
+        <v>-206.12293515</v>
       </c>
       <c r="Q92">
-        <v>-201.8447985</v>
+        <v>-204.62293515</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2648708406817206</v>
+        <v>0.2892120452019117</v>
       </c>
       <c r="T92">
-        <v>4.270098441228067</v>
+        <v>4.744553823586742</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04668146903428957</v>
+        <v>0.0461684858580886</v>
       </c>
       <c r="W92">
-        <v>0.2247925096017145</v>
+        <v>0.2249134710346627</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1867258761371583</v>
+        <v>0.1846739434323543</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2307003427097152</v>
+        <v>0.2326003427097151</v>
       </c>
       <c r="C93">
-        <v>-954.1456408289162</v>
+        <v>-971.3831143760376</v>
       </c>
       <c r="D93">
-        <v>150.2733591710841</v>
+        <v>148.7448856239625</v>
       </c>
       <c r="E93">
-        <v>1190.819</v>
+        <v>1206.528</v>
       </c>
       <c r="F93">
-        <v>1429.519</v>
+        <v>1445.228</v>
       </c>
       <c r="G93">
         <v>325.1</v>
@@ -9169,37 +9169,37 @@
         <v>62.25</v>
       </c>
       <c r="M93">
-        <v>337.0805802</v>
+        <v>340.7847624</v>
       </c>
       <c r="N93">
-        <v>-274.8305802</v>
+        <v>-278.5347624</v>
       </c>
       <c r="O93">
-        <v>-68.70764505000001</v>
+        <v>-69.63369060000001</v>
       </c>
       <c r="P93">
-        <v>-206.12293515</v>
+        <v>-208.9010718</v>
       </c>
       <c r="Q93">
-        <v>-204.62293515</v>
+        <v>-207.4010718</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2892120452019117</v>
+        <v>0.3196385508521508</v>
       </c>
       <c r="T93">
-        <v>4.744553823586742</v>
+        <v>5.337623051535087</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0461684858580886</v>
+        <v>0.04566665449006589</v>
       </c>
       <c r="W93">
-        <v>0.2249134710346627</v>
+        <v>0.2250318028712425</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1846739434323543</v>
+        <v>0.1826666179602636</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2326003427097151</v>
+        <v>0.2345003427097151</v>
       </c>
       <c r="C94">
-        <v>-971.3831143760376</v>
+        <v>-988.5898079076296</v>
       </c>
       <c r="D94">
-        <v>148.7448856239625</v>
+        <v>147.2471920923705</v>
       </c>
       <c r="E94">
-        <v>1206.528</v>
+        <v>1222.237</v>
       </c>
       <c r="F94">
-        <v>1445.228</v>
+        <v>1460.937</v>
       </c>
       <c r="G94">
         <v>325.1</v>
@@ -9251,37 +9251,37 @@
         <v>62.25</v>
       </c>
       <c r="M94">
-        <v>340.7847624</v>
+        <v>344.4889446</v>
       </c>
       <c r="N94">
-        <v>-278.5347624</v>
+        <v>-282.2389446</v>
       </c>
       <c r="O94">
-        <v>-69.63369060000001</v>
+        <v>-70.55973615000001</v>
       </c>
       <c r="P94">
-        <v>-208.9010718</v>
+        <v>-211.67920845</v>
       </c>
       <c r="Q94">
-        <v>-207.4010718</v>
+        <v>-210.17920845</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3196385508521508</v>
+        <v>0.3587583438310296</v>
       </c>
       <c r="T94">
-        <v>5.337623051535087</v>
+        <v>6.100140630325814</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04566665449006589</v>
+        <v>0.04517561519447379</v>
       </c>
       <c r="W94">
-        <v>0.2250318028712425</v>
+        <v>0.2251475899371431</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1826666179602636</v>
+        <v>0.1807024607778952</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2345003427097151</v>
+        <v>0.2364003427097151</v>
       </c>
       <c r="C95">
-        <v>-988.5898079076296</v>
+        <v>-1005.766641915681</v>
       </c>
       <c r="D95">
-        <v>147.2471920923705</v>
+        <v>145.7793580843195</v>
       </c>
       <c r="E95">
-        <v>1222.237</v>
+        <v>1237.946</v>
       </c>
       <c r="F95">
-        <v>1460.937</v>
+        <v>1476.646</v>
       </c>
       <c r="G95">
         <v>325.1</v>
@@ -9333,37 +9333,37 @@
         <v>62.25</v>
       </c>
       <c r="M95">
-        <v>344.4889446</v>
+        <v>348.1931268000001</v>
       </c>
       <c r="N95">
-        <v>-282.2389446</v>
+        <v>-285.9431268000001</v>
       </c>
       <c r="O95">
-        <v>-70.55973615000001</v>
+        <v>-71.48578170000002</v>
       </c>
       <c r="P95">
-        <v>-211.67920845</v>
+        <v>-214.4573451000001</v>
       </c>
       <c r="Q95">
-        <v>-210.17920845</v>
+        <v>-212.9573451000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3587583438310296</v>
+        <v>0.4109180678028679</v>
       </c>
       <c r="T95">
-        <v>6.100140630325814</v>
+        <v>7.116830735380118</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04517561519447379</v>
+        <v>0.04469502354346874</v>
       </c>
       <c r="W95">
-        <v>0.2251475899371431</v>
+        <v>0.2252609134484501</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1807024607778952</v>
+        <v>0.178780094173875</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2364003427097151</v>
+        <v>0.2383003427097152</v>
       </c>
       <c r="C96">
-        <v>-1005.766641915681</v>
+        <v>-1022.914500550742</v>
       </c>
       <c r="D96">
-        <v>145.7793580843195</v>
+        <v>144.3404994492577</v>
       </c>
       <c r="E96">
-        <v>1237.946</v>
+        <v>1253.655</v>
       </c>
       <c r="F96">
-        <v>1476.646</v>
+        <v>1492.355</v>
       </c>
       <c r="G96">
         <v>325.1</v>
@@ -9415,37 +9415,37 @@
         <v>62.25</v>
       </c>
       <c r="M96">
-        <v>348.1931268000001</v>
+        <v>351.8973090000001</v>
       </c>
       <c r="N96">
-        <v>-285.9431268000001</v>
+        <v>-289.6473090000001</v>
       </c>
       <c r="O96">
-        <v>-71.48578170000002</v>
+        <v>-72.41182725000002</v>
       </c>
       <c r="P96">
-        <v>-214.4573451000001</v>
+        <v>-217.23548175</v>
       </c>
       <c r="Q96">
-        <v>-212.9573451000001</v>
+        <v>-215.73548175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4109180678028679</v>
+        <v>0.4839416813634416</v>
       </c>
       <c r="T96">
-        <v>7.116830735380118</v>
+        <v>8.540196882456145</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04469502354346874</v>
+        <v>0.04422454961143223</v>
       </c>
       <c r="W96">
-        <v>0.2252609134484501</v>
+        <v>0.2253718512016243</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.178780094173875</v>
+        <v>0.176898198445729</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2383003427097152</v>
+        <v>0.2402003427097151</v>
       </c>
       <c r="C97">
-        <v>-1022.914500550742</v>
+        <v>-1040.034233397871</v>
       </c>
       <c r="D97">
-        <v>144.3404994492577</v>
+        <v>142.9297666021295</v>
       </c>
       <c r="E97">
-        <v>1253.655</v>
+        <v>1269.364</v>
       </c>
       <c r="F97">
-        <v>1492.355</v>
+        <v>1508.064</v>
       </c>
       <c r="G97">
         <v>325.1</v>
@@ -9497,37 +9497,37 @@
         <v>62.25</v>
       </c>
       <c r="M97">
-        <v>351.8973090000001</v>
+        <v>355.6014912000001</v>
       </c>
       <c r="N97">
-        <v>-289.6473090000001</v>
+        <v>-293.3514912000001</v>
       </c>
       <c r="O97">
-        <v>-72.41182725000002</v>
+        <v>-73.33787280000003</v>
       </c>
       <c r="P97">
-        <v>-217.23548175</v>
+        <v>-220.0136184000001</v>
       </c>
       <c r="Q97">
-        <v>-215.73548175</v>
+        <v>-218.5136184000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4839416813634416</v>
+        <v>0.5934771017043022</v>
       </c>
       <c r="T97">
-        <v>8.540196882456145</v>
+        <v>10.67524610307019</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04422454961143223</v>
+        <v>0.04376387721964647</v>
       </c>
       <c r="W97">
-        <v>0.2253718512016243</v>
+        <v>0.2254804777516074</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.176898198445729</v>
+        <v>0.1750555088785859</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2402003427097151</v>
+        <v>0.2421003427097151</v>
       </c>
       <c r="C98">
-        <v>-1040.034233397871</v>
+        <v>-1057.126657149431</v>
       </c>
       <c r="D98">
-        <v>142.9297666021295</v>
+        <v>141.5463428505692</v>
       </c>
       <c r="E98">
-        <v>1269.364</v>
+        <v>1285.073</v>
       </c>
       <c r="F98">
-        <v>1508.064</v>
+        <v>1523.773</v>
       </c>
       <c r="G98">
         <v>325.1</v>
@@ -9579,37 +9579,37 @@
         <v>62.25</v>
       </c>
       <c r="M98">
-        <v>355.6014912000001</v>
+        <v>359.3056734</v>
       </c>
       <c r="N98">
-        <v>-293.3514912000001</v>
+        <v>-297.0556734</v>
       </c>
       <c r="O98">
-        <v>-73.33787280000001</v>
+        <v>-74.26391835000001</v>
       </c>
       <c r="P98">
-        <v>-220.0136184</v>
+        <v>-222.79175505</v>
       </c>
       <c r="Q98">
-        <v>-218.5136184</v>
+        <v>-221.29175505</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5934771017043008</v>
+        <v>0.7760361356057345</v>
       </c>
       <c r="T98">
-        <v>10.67524610307016</v>
+        <v>14.23366147076021</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04376387721964648</v>
+        <v>0.04331270322769136</v>
       </c>
       <c r="W98">
-        <v>0.2254804777516074</v>
+        <v>0.2255868645789104</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1750555088785859</v>
+        <v>0.1732508129107655</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2421003427097151</v>
+        <v>0.2440003427097151</v>
       </c>
       <c r="C99">
-        <v>-1057.126657149431</v>
+        <v>-1074.192557181687</v>
       </c>
       <c r="D99">
-        <v>141.5463428505692</v>
+        <v>140.1894428183127</v>
       </c>
       <c r="E99">
-        <v>1285.073</v>
+        <v>1300.782</v>
       </c>
       <c r="F99">
-        <v>1523.773</v>
+        <v>1539.482</v>
       </c>
       <c r="G99">
         <v>325.1</v>
@@ -9661,37 +9661,37 @@
         <v>62.25</v>
       </c>
       <c r="M99">
-        <v>359.3056734</v>
+        <v>363.0098556</v>
       </c>
       <c r="N99">
-        <v>-297.0556734</v>
+        <v>-300.7598556</v>
       </c>
       <c r="O99">
-        <v>-74.26391835000001</v>
+        <v>-75.1899639</v>
       </c>
       <c r="P99">
-        <v>-222.79175505</v>
+        <v>-225.5698917</v>
       </c>
       <c r="Q99">
-        <v>-221.29175505</v>
+        <v>-224.0698917</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7760361356057345</v>
+        <v>1.141154203408602</v>
       </c>
       <c r="T99">
-        <v>14.23366147076021</v>
+        <v>21.35049220614032</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04331270322769136</v>
+        <v>0.04287073686822513</v>
       </c>
       <c r="W99">
-        <v>0.2255868645789104</v>
+        <v>0.2256910802464725</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1732508129107655</v>
+        <v>0.1714829474729005</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2440003427097151</v>
+        <v>0.2459003427097151</v>
       </c>
       <c r="C100">
-        <v>-1074.192557181687</v>
+        <v>-1091.232689041572</v>
       </c>
       <c r="D100">
-        <v>140.1894428183127</v>
+        <v>138.8583109584277</v>
       </c>
       <c r="E100">
-        <v>1300.782</v>
+        <v>1316.491</v>
       </c>
       <c r="F100">
-        <v>1539.482</v>
+        <v>1555.191</v>
       </c>
       <c r="G100">
         <v>325.1</v>
@@ -9743,37 +9743,37 @@
         <v>62.25</v>
       </c>
       <c r="M100">
-        <v>363.0098556</v>
+        <v>366.7140378</v>
       </c>
       <c r="N100">
-        <v>-300.7598556</v>
+        <v>-304.4640378</v>
       </c>
       <c r="O100">
-        <v>-75.1899639</v>
+        <v>-76.11600945000001</v>
       </c>
       <c r="P100">
-        <v>-225.5698917</v>
+        <v>-228.34802835</v>
       </c>
       <c r="Q100">
-        <v>-224.0698917</v>
+        <v>-226.84802835</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.141154203408602</v>
+        <v>2.236508406817203</v>
       </c>
       <c r="T100">
-        <v>21.35049220614032</v>
+        <v>42.70098441228063</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04287073686822513</v>
+        <v>0.04243769912208144</v>
       </c>
       <c r="W100">
-        <v>0.2256910802464725</v>
+        <v>0.2257931905470132</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1714829474729005</v>
+        <v>0.1697507964883257</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2459003427097151</v>
-      </c>
-      <c r="C101">
-        <v>-1091.232689041572</v>
-      </c>
-      <c r="D101">
-        <v>138.8583109584277</v>
-      </c>
-      <c r="E101">
-        <v>1316.491</v>
-      </c>
-      <c r="F101">
-        <v>1555.191</v>
-      </c>
-      <c r="G101">
-        <v>325.1</v>
-      </c>
-      <c r="H101">
-        <v>1332.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>63.75</v>
-      </c>
-      <c r="K101">
-        <v>1.5</v>
-      </c>
-      <c r="L101">
-        <v>62.25</v>
-      </c>
-      <c r="M101">
-        <v>366.7140378</v>
-      </c>
-      <c r="N101">
-        <v>-304.4640378</v>
-      </c>
-      <c r="O101">
-        <v>-76.11600945000001</v>
-      </c>
-      <c r="P101">
-        <v>-228.34802835</v>
-      </c>
-      <c r="Q101">
-        <v>-226.84802835</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.236508406817203</v>
-      </c>
-      <c r="T101">
-        <v>42.70098441228063</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04243769912208144</v>
-      </c>
-      <c r="W101">
-        <v>0.2257931905470132</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1697507964883257</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
